--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -11,29 +11,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дорожная карта" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кварталы" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Квартальный roadmap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Релизы" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вехи" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Технический долг" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ретроспективы" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OKR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ёмкость на горизонт" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гант" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Капасити" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Календарь" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Загрузка по ролям" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бэклог" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сгорание" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Качество" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баги" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFD" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Метрики и прогноз" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cycle time" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Риски" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица рисков" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RICE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Квартальный roadmap" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Релизы" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вехи" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Технический долг" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ретроспективы" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OKR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ёмкость на горизонт" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гант" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Капасити" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Календарь" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Загрузка по ролям" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бэклог" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сгорание" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Качество" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баги" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFD" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Метрики и прогноз" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cycle time" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Риски" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица рисков" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -42,14 +43,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="dd\.mm"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="dd\.mm\.yy"/>
+    <numFmt numFmtId="169" formatCode="# ##0"/>
+    <numFmt numFmtId="170" formatCode="# ##0.0"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -339,6 +342,21 @@
       <color rgb="FF1F4E78"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF5A6B82"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="51">
     <fill>
@@ -593,7 +611,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -839,11 +857,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1399,11 +1431,30 @@
     <xf numFmtId="167" fontId="16" fillId="50" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="42">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1674,6 +1725,27 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8D7DA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13434,6 +13506,87 @@
       <tx>
         <rich>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>RICE score по фичам</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'RICE'!G4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'RICE'!$B$5:$B$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RICE'!$G$5:$G$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart44.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
@@ -13854,7 +14007,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart45.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -14151,7 +14304,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart46.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -14285,7 +14438,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart47.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -14436,7 +14589,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart48.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -14575,7 +14728,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -15001,201 +15154,6 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart49.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Расход бюджета (накопл.)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <layout/>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Бюджет!$D$6</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Накопл. стоимость (₽)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>Бюджет!$A$7:$A$17</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Бюджет!$D$7:$D$17</f>
-              <numCache>
-                <formatCode>#,##0</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>742400.0000000001</v>
-                </pt>
-                <pt idx="1">
-                  <v>1504000</v>
-                </pt>
-                <pt idx="2">
-                  <v>2265600</v>
-                </pt>
-                <pt idx="3">
-                  <v>3027200</v>
-                </pt>
-                <pt idx="4">
-                  <v>3772800</v>
-                </pt>
-                <pt idx="5">
-                  <v>4534400</v>
-                </pt>
-                <pt idx="6">
-                  <v>5219840</v>
-                </pt>
-                <pt idx="7">
-                  <v>5949440</v>
-                </pt>
-                <pt idx="8">
-                  <v>6711040</v>
-                </pt>
-                <pt idx="9">
-                  <v>7472640</v>
-                </pt>
-                <pt idx="10">
-                  <v>8158080</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <smooth val="0"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="100"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="#,##0" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="10"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -15807,6 +15765,201 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
+              <a:t>Расход бюджета (накопл.)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Бюджет!$D$6</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Накопл. стоимость (₽)</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Бюджет!$A$7:$A$17</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>5</v>
+                </pt>
+                <pt idx="5">
+                  <v>6</v>
+                </pt>
+                <pt idx="6">
+                  <v>7</v>
+                </pt>
+                <pt idx="7">
+                  <v>8</v>
+                </pt>
+                <pt idx="8">
+                  <v>9</v>
+                </pt>
+                <pt idx="9">
+                  <v>10</v>
+                </pt>
+                <pt idx="10">
+                  <v>11</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Бюджет!$D$7:$D$17</f>
+              <numCache>
+                <formatCode>#,##0</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>742400.0000000001</v>
+                </pt>
+                <pt idx="1">
+                  <v>1504000</v>
+                </pt>
+                <pt idx="2">
+                  <v>2265600</v>
+                </pt>
+                <pt idx="3">
+                  <v>3027200</v>
+                </pt>
+                <pt idx="4">
+                  <v>3772800</v>
+                </pt>
+                <pt idx="5">
+                  <v>4534400</v>
+                </pt>
+                <pt idx="6">
+                  <v>5219840</v>
+                </pt>
+                <pt idx="7">
+                  <v>5949440</v>
+                </pt>
+                <pt idx="8">
+                  <v>6711040</v>
+                </pt>
+                <pt idx="9">
+                  <v>7472640</v>
+                </pt>
+                <pt idx="10">
+                  <v>8158080</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t xml:space="preserve">Прогресс </a:t>
             </a:r>
             <a:r>
@@ -15948,7 +16101,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart52.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -16158,7 +16311,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart53.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -16954,7 +17107,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart54.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -17252,7 +17405,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -17626,7 +17779,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18010,7 +18163,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18368,7 +18521,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18669,7 +18822,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18852,162 +19005,6 @@
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Доля багов по спринтам</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="1"/>
-    </title>
-    <plotArea>
-      <layout/>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="1"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>Баги!$J$6:$J$16</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Баги!$P$6:$P$16</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>5</v>
-                </pt>
-                <pt idx="1">
-                  <v>6</v>
-                </pt>
-                <pt idx="2">
-                  <v>2</v>
-                </pt>
-                <pt idx="3">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="4">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="5">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="6">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="7">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="8">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="9">
-                  <v>#N/A</v>
-                </pt>
-                <pt idx="10">
-                  <v>#N/A</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="1"/>
-          <showBubbleSize val="1"/>
-          <showLeaderLines val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-    </legend>
-    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
@@ -19278,6 +19275,162 @@
 </file>
 
 <file path=xl/charts/chart60.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Доля багов по спринтам</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="1"/>
+            <showBubbleSize val="1"/>
+            <showLeaderLines val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>Баги!$J$6:$J$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>5</v>
+                </pt>
+                <pt idx="5">
+                  <v>6</v>
+                </pt>
+                <pt idx="6">
+                  <v>7</v>
+                </pt>
+                <pt idx="7">
+                  <v>8</v>
+                </pt>
+                <pt idx="8">
+                  <v>9</v>
+                </pt>
+                <pt idx="9">
+                  <v>10</v>
+                </pt>
+                <pt idx="10">
+                  <v>11</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Баги!$P$6:$P$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>5</v>
+                </pt>
+                <pt idx="1">
+                  <v>6</v>
+                </pt>
+                <pt idx="2">
+                  <v>2</v>
+                </pt>
+                <pt idx="3">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="4">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="5">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="6">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="7">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="8">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="9">
+                  <v>#N/A</v>
+                </pt>
+                <pt idx="10">
+                  <v>#N/A</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="1"/>
+          <showBubbleSize val="1"/>
+          <showLeaderLines val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -19738,7 +19891,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -19935,7 +20088,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart63.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20127,7 +20280,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart64.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20379,7 +20532,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart65.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20631,7 +20784,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart66.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20950,7 +21103,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart67.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -21715,7 +21868,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart68.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -21916,7 +22069,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart69.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -22061,7 +22214,147 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>% выполнения по кварталам</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Кварталы!$G$4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>% выпол-
+нения</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <strRef>
+              <f>Кварталы!$A$5:$A$7</f>
+              <strCache>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>Q3 2026</v>
+                </pt>
+                <pt idx="1">
+                  <v>Q4 2026</v>
+                </pt>
+                <pt idx="2">
+                  <v>Q1 2027</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Кварталы!$G$5:$G$7</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>0.3551401869158878</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart70.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -22294,147 +22587,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>% выполнения по кварталам</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Кварталы!$G$4</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>% выпол-
-нения</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="1"/>
-          <cat>
-            <strRef>
-              <f>Кварталы!$A$5:$A$7</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>Q3 2026</v>
-                </pt>
-                <pt idx="1">
-                  <v>Q4 2026</v>
-                </pt>
-                <pt idx="2">
-                  <v>Q1 2027</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Кварталы!$G$5:$G$7</f>
-              <numCache>
-                <formatCode>0%</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>0.3551401869158878</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="100"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="10"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart71.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -24402,6 +24555,33 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>8</col>
       <colOff>0</colOff>
       <row>3</row>
@@ -24425,7 +24605,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24452,7 +24632,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24479,7 +24659,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24506,7 +24686,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24555,7 +24735,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24582,7 +24762,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24653,7 +24833,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24680,7 +24860,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24795,33 +24975,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>541020</colOff>
-      <row>9</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <ext cx="7920000" cy="3240000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -24875,6 +25028,33 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>5</col>
+      <colOff>541020</colOff>
+      <row>9</row>
+      <rowOff>38100</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>10</col>
       <colOff>0</colOff>
       <row>3</row>
@@ -24898,7 +25078,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24955,7 +25135,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24982,7 +25162,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25133,6 +25313,33 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>6</col>
       <colOff>0</colOff>
       <row>3</row>
@@ -25156,7 +25363,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25183,7 +25390,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25210,7 +25417,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25273,33 +25480,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6120000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -25845,6 +26025,771 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="16.6640625" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10.77734375" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" customHeight="1">
+      <c r="A1" s="198" t="inlineStr">
+        <is>
+          <t>Технический долг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="199" t="inlineStr">
+        <is>
+          <t>Реестр техдолга: область, тип, влияние, оценка, план спринта, статус.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="41.4" customHeight="1">
+      <c r="A4" s="200" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="200" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="C4" s="200" t="inlineStr">
+        <is>
+          <t>Область</t>
+        </is>
+      </c>
+      <c r="D4" s="200" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="E4" s="200" t="inlineStr">
+        <is>
+          <t>Влияние</t>
+        </is>
+      </c>
+      <c r="F4" s="200" t="inlineStr">
+        <is>
+          <t>Оценка (дн)</t>
+        </is>
+      </c>
+      <c r="G4" s="200" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="H4" s="200" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="I4" s="200" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="J4" s="200" t="inlineStr">
+        <is>
+          <t>Спринт
+создан</t>
+        </is>
+      </c>
+      <c r="K4" s="200" t="inlineStr">
+        <is>
+          <t>Спринт
+погашен</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27.6" customHeight="1">
+      <c r="A5" s="201" t="inlineStr">
+        <is>
+          <t>TD-1</t>
+        </is>
+      </c>
+      <c r="B5" s="202" t="inlineStr">
+        <is>
+          <t>Рефакторинг модуля авторизации</t>
+        </is>
+      </c>
+      <c r="C5" s="201" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D5" s="201" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="E5" s="201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="201" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="201" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="J5" s="212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="212" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="27.6" customHeight="1">
+      <c r="A6" s="201" t="inlineStr">
+        <is>
+          <t>TD-2</t>
+        </is>
+      </c>
+      <c r="B6" s="202" t="inlineStr">
+        <is>
+          <t>Автотесты оформления заказа</t>
+        </is>
+      </c>
+      <c r="C6" s="201" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="D6" s="201" t="inlineStr">
+        <is>
+          <t>Тесты</t>
+        </is>
+      </c>
+      <c r="E6" s="201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="201" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="J6" s="212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="212" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="201" t="inlineStr">
+        <is>
+          <t>TD-3</t>
+        </is>
+      </c>
+      <c r="B7" s="202" t="inlineStr">
+        <is>
+          <t>Убрать дубли в API заказов</t>
+        </is>
+      </c>
+      <c r="C7" s="201" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D7" s="201" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="E7" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H7" s="201" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="201" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="J7" s="212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="212" t="n"/>
+    </row>
+    <row r="8" ht="27.6" customHeight="1">
+      <c r="A8" s="201" t="inlineStr">
+        <is>
+          <t>TD-4</t>
+        </is>
+      </c>
+      <c r="B8" s="202" t="inlineStr">
+        <is>
+          <t>Обновить документацию API</t>
+        </is>
+      </c>
+      <c r="C8" s="201" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D8" s="201" t="inlineStr">
+        <is>
+          <t>Документация</t>
+        </is>
+      </c>
+      <c r="E8" s="201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F8" s="210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="201" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H8" s="201" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="201" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="J8" s="212" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="212" t="n"/>
+    </row>
+    <row r="9" ht="27.6" customHeight="1">
+      <c r="A9" s="201" t="inlineStr">
+        <is>
+          <t>TD-5</t>
+        </is>
+      </c>
+      <c r="B9" s="202" t="inlineStr">
+        <is>
+          <t>Мониторинг и алерты платежей</t>
+        </is>
+      </c>
+      <c r="C9" s="201" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="D9" s="201" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E9" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" s="210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H9" s="201" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="201" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="J9" s="212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="212" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="201" t="inlineStr">
+        <is>
+          <t>TD-6</t>
+        </is>
+      </c>
+      <c r="B10" s="202" t="inlineStr">
+        <is>
+          <t>Оптимизация запросов БД</t>
+        </is>
+      </c>
+      <c r="C10" s="201" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="D10" s="201" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="E10" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H10" s="201" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="201" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="J10" s="212" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="212" t="n"/>
+    </row>
+    <row r="12" ht="15.6" customHeight="1">
+      <c r="A12" s="207" t="inlineStr">
+        <is>
+          <t>По типу</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="200" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="B13" s="200" t="inlineStr">
+        <is>
+          <t>Оценка (дн)</t>
+        </is>
+      </c>
+      <c r="C13" s="200" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27.6" customHeight="1">
+      <c r="A14" s="208" t="inlineStr">
+        <is>
+          <t>Архитектура</t>
+        </is>
+      </c>
+      <c r="B14" s="206">
+        <f>SUMIF($D$5:$D$10,A14,$F$5:$F$10)</f>
+        <v/>
+      </c>
+      <c r="C14" s="205">
+        <f>COUNTIF($D$5:$D$10,A14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="208" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B15" s="206">
+        <f>SUMIF($D$5:$D$10,A15,$F$5:$F$10)</f>
+        <v/>
+      </c>
+      <c r="C15" s="205">
+        <f>COUNTIF($D$5:$D$10,A15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="208" t="inlineStr">
+        <is>
+          <t>Тесты</t>
+        </is>
+      </c>
+      <c r="B16" s="206">
+        <f>SUMIF($D$5:$D$10,A16,$F$5:$F$10)</f>
+        <v/>
+      </c>
+      <c r="C16" s="205">
+        <f>COUNTIF($D$5:$D$10,A16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="208" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="B17" s="206">
+        <f>SUMIF($D$5:$D$10,A17,$F$5:$F$10)</f>
+        <v/>
+      </c>
+      <c r="C17" s="205">
+        <f>COUNTIF($D$5:$D$10,A17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="208" t="inlineStr">
+        <is>
+          <t>Документация</t>
+        </is>
+      </c>
+      <c r="B18" s="206">
+        <f>SUMIF($D$5:$D$10,A18,$F$5:$F$10)</f>
+        <v/>
+      </c>
+      <c r="C18" s="205">
+        <f>COUNTIF($D$5:$D$10,A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15.6" customHeight="1">
+      <c r="A20" s="207" t="inlineStr">
+        <is>
+          <t>По статусу</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="200" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="B21" s="200" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="208" t="inlineStr">
+        <is>
+          <t>Открыт</t>
+        </is>
+      </c>
+      <c r="B22" s="205">
+        <f>COUNTIF($I$5:$I$10,A22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="208" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="B23" s="205">
+        <f>COUNTIF($I$5:$I$10,A23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="208" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="B24" s="205">
+        <f>COUNTIF($I$5:$I$10,A24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15.6" customHeight="1">
+      <c r="A27" s="207" t="inlineStr">
+        <is>
+          <t>Тренд техдолга (создано / погашено по спринтам)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27.6" customHeight="1">
+      <c r="A28" s="200" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="B28" s="200" t="inlineStr">
+        <is>
+          <t>Создано</t>
+        </is>
+      </c>
+      <c r="C28" s="200" t="inlineStr">
+        <is>
+          <t>Погашено</t>
+        </is>
+      </c>
+      <c r="D28" s="200" t="inlineStr">
+        <is>
+          <t>Открыто (накопит.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="208" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="205">
+        <f>COUNTIF($J$5:$J$10,A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="205">
+        <f>COUNTIF($K$5:$K$10,A29)</f>
+        <v/>
+      </c>
+      <c r="D29" s="209">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="208" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="205">
+        <f>COUNTIF($J$5:$J$10,A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="205">
+        <f>COUNTIF($K$5:$K$10,A30)</f>
+        <v/>
+      </c>
+      <c r="D30" s="209">
+        <f>D29+B30-C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="208" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="205">
+        <f>COUNTIF($J$5:$J$10,A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="205">
+        <f>COUNTIF($K$5:$K$10,A31)</f>
+        <v/>
+      </c>
+      <c r="D31" s="209">
+        <f>D30+B31-C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="208" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="205">
+        <f>COUNTIF($J$5:$J$10,A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="205">
+        <f>COUNTIF($K$5:$K$10,A32)</f>
+        <v/>
+      </c>
+      <c r="D32" s="209">
+        <f>D31+B32-C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="208" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="205">
+        <f>COUNTIF($J$5:$J$10,A33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="205">
+        <f>COUNTIF($K$5:$K$10,A33)</f>
+        <v/>
+      </c>
+      <c r="D33" s="209">
+        <f>D32+B33-C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="208" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="205">
+        <f>COUNTIF($J$5:$J$10,A34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="205">
+        <f>COUNTIF($K$5:$K$10,A34)</f>
+        <v/>
+      </c>
+      <c r="D34" s="209">
+        <f>D33+B34-C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="208" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="205">
+        <f>COUNTIF($J$5:$J$10,A35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="205">
+        <f>COUNTIF($K$5:$K$10,A35)</f>
+        <v/>
+      </c>
+      <c r="D35" s="209">
+        <f>D34+B35-C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="208" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="205">
+        <f>COUNTIF($J$5:$J$10,A36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="205">
+        <f>COUNTIF($K$5:$K$10,A36)</f>
+        <v/>
+      </c>
+      <c r="D36" s="209">
+        <f>D35+B36-C36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="208" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="205">
+        <f>COUNTIF($J$5:$J$10,A37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="205">
+        <f>COUNTIF($K$5:$K$10,A37)</f>
+        <v/>
+      </c>
+      <c r="D37" s="209">
+        <f>D36+B37-C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="208" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" s="205">
+        <f>COUNTIF($J$5:$J$10,A38)</f>
+        <v/>
+      </c>
+      <c r="C38" s="205">
+        <f>COUNTIF($K$5:$K$10,A38)</f>
+        <v/>
+      </c>
+      <c r="D38" s="209">
+        <f>D37+B38-C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="208" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="205">
+        <f>COUNTIF($J$5:$J$10,A39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="205">
+        <f>COUNTIF($K$5:$K$10,A39)</f>
+        <v/>
+      </c>
+      <c r="D39" s="209">
+        <f>D38+B39-C39</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Архитектура,Код,Тесты,Инфраструктура,Документация"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5 I6 I7 I8 I9 I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Открыт,В работе,Закрыт"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -26079,7 +27024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26469,7 +27414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26711,7 +27656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27067,7 +28012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28817,7 +29762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33719,7 +34664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33881,7 +34826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34538,7 +35483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37285,448 +38230,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="19.33203125" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Диаграмма сгорания (burndown) по задачам</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Идеальная линия — равномерное сгорание. Фактический остаток обновляется каждый день (жёлтый столбец).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Всего работы тек. спринта (дн):</t>
-        </is>
-      </c>
-      <c r="B3" s="25">
-        <f>SUMIF(Бэклог!$M$5:$M$44,Параметры!$B$13,Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Рабочих дней:</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <f>SUMIF('Дорожная карта'!$A$6:$A$16,Параметры!$B$13,'Дорожная карта'!$E$6:$E$16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="27.6" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>День</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Идеальный остаток (дн)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Факт. остаток (дн)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="B7" s="22">
-        <f>WORKDAY(Параметры!$B$6,A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="23">
-        <f>$B$3*($B$4-A7)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>$B$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="22">
-        <f>WORKDAY(Параметры!$B$6,A8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="23">
-        <f>$B$3*($B$4-A8)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>ROUND($B$3*0.98,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="22">
-        <f>WORKDAY(Параметры!$B$6,A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="23">
-        <f>$B$3*($B$4-A9)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D9" s="24">
-        <f>ROUND($B$3*0.9,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="22">
-        <f>WORKDAY(Параметры!$B$6,A10)</f>
-        <v/>
-      </c>
-      <c r="C10" s="23">
-        <f>$B$3*($B$4-A10)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>ROUND($B$3*0.86,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="22">
-        <f>WORKDAY(Параметры!$B$6,A11)</f>
-        <v/>
-      </c>
-      <c r="C11" s="23">
-        <f>$B$3*($B$4-A11)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>ROUND($B$3*0.72,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="22">
-        <f>WORKDAY(Параметры!$B$6,A12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="23">
-        <f>$B$3*($B$4-A12)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>ROUND($B$3*0.6,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="22">
-        <f>WORKDAY(Параметры!$B$6,A13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="23">
-        <f>$B$3*($B$4-A13)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>ROUND($B$3*0.55,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="22">
-        <f>WORKDAY(Параметры!$B$6,A14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="23">
-        <f>$B$3*($B$4-A14)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>ROUND($B$3*0.4,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="22">
-        <f>WORKDAY(Параметры!$B$6,A15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="23">
-        <f>$B$3*($B$4-A15)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>ROUND($B$3*0.28,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="22">
-        <f>WORKDAY(Параметры!$B$6,A16)</f>
-        <v/>
-      </c>
-      <c r="C16" s="23">
-        <f>$B$3*($B$4-A16)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D16" s="24">
-        <f>ROUND($B$3*0.12,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="22">
-        <f>WORKDAY(Параметры!$B$6,A17)</f>
-        <v/>
-      </c>
-      <c r="C17" s="23">
-        <f>$B$3*($B$4-A17)/$B$4</f>
-        <v/>
-      </c>
-      <c r="D17" s="24">
-        <f>ROUND($B$3*0,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Как читать:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.6" customHeight="1">
-      <c r="A20" s="91" t="inlineStr">
-        <is>
-          <t>Burn-up: объём vs накопленно сделано</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="41.4" customHeight="1">
-      <c r="A21" s="92" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="B21" s="92" t="inlineStr">
-        <is>
-          <t>Накопл.
-сделано (дн)</t>
-        </is>
-      </c>
-      <c r="C21" s="92" t="inlineStr">
-        <is>
-          <t>Общий
-объём (дн)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="110" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A22)</f>
-        <v/>
-      </c>
-      <c r="C22" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="110" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A23)</f>
-        <v/>
-      </c>
-      <c r="C23" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="110" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A24)</f>
-        <v/>
-      </c>
-      <c r="C24" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="110" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A25)</f>
-        <v/>
-      </c>
-      <c r="C25" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="110" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A26)</f>
-        <v/>
-      </c>
-      <c r="C26" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="110" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A27)</f>
-        <v/>
-      </c>
-      <c r="C27" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="110" t="n">
-        <v>7</v>
-      </c>
-      <c r="B28" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A28)</f>
-        <v/>
-      </c>
-      <c r="C28" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="110" t="n">
-        <v>8</v>
-      </c>
-      <c r="B29" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A29)</f>
-        <v/>
-      </c>
-      <c r="C29" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="110" t="n">
-        <v>9</v>
-      </c>
-      <c r="B30" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A30)</f>
-        <v/>
-      </c>
-      <c r="C30" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="110" t="n">
-        <v>10</v>
-      </c>
-      <c r="B31" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A31)</f>
-        <v/>
-      </c>
-      <c r="C31" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="110" t="n">
-        <v>11</v>
-      </c>
-      <c r="B32" s="102">
-        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A32)</f>
-        <v/>
-      </c>
-      <c r="C32" s="102">
-        <f>SUM(Бэклог!$E$5:$E$44)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -38169,6 +38672,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="19.33203125" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Диаграмма сгорания (burndown) по задачам</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Идеальная линия — равномерное сгорание. Фактический остаток обновляется каждый день (жёлтый столбец).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Всего работы тек. спринта (дн):</t>
+        </is>
+      </c>
+      <c r="B3" s="25">
+        <f>SUMIF(Бэклог!$M$5:$M$44,Параметры!$B$13,Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Рабочих дней:</t>
+        </is>
+      </c>
+      <c r="B4" s="15">
+        <f>SUMIF('Дорожная карта'!$A$6:$A$16,Параметры!$B$13,'Дорожная карта'!$E$6:$E$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="27.6" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Идеальный остаток (дн)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Факт. остаток (дн)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="22">
+        <f>WORKDAY(Параметры!$B$6,A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="23">
+        <f>$B$3*($B$4-A7)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="22">
+        <f>WORKDAY(Параметры!$B$6,A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="23">
+        <f>$B$3*($B$4-A8)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>ROUND($B$3*0.98,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="22">
+        <f>WORKDAY(Параметры!$B$6,A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="23">
+        <f>$B$3*($B$4-A9)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>ROUND($B$3*0.9,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="22">
+        <f>WORKDAY(Параметры!$B$6,A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="23">
+        <f>$B$3*($B$4-A10)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>ROUND($B$3*0.86,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="22">
+        <f>WORKDAY(Параметры!$B$6,A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="23">
+        <f>$B$3*($B$4-A11)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>ROUND($B$3*0.72,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="22">
+        <f>WORKDAY(Параметры!$B$6,A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="23">
+        <f>$B$3*($B$4-A12)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>ROUND($B$3*0.6,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="22">
+        <f>WORKDAY(Параметры!$B$6,A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="23">
+        <f>$B$3*($B$4-A13)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>ROUND($B$3*0.55,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="22">
+        <f>WORKDAY(Параметры!$B$6,A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="23">
+        <f>$B$3*($B$4-A14)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>ROUND($B$3*0.4,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="22">
+        <f>WORKDAY(Параметры!$B$6,A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="23">
+        <f>$B$3*($B$4-A15)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>ROUND($B$3*0.28,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="22">
+        <f>WORKDAY(Параметры!$B$6,A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="23">
+        <f>$B$3*($B$4-A16)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>ROUND($B$3*0.12,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="22">
+        <f>WORKDAY(Параметры!$B$6,A17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="23">
+        <f>$B$3*($B$4-A17)/$B$4</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>ROUND($B$3*0,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Как читать:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.6" customHeight="1">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>Burn-up: объём vs накопленно сделано</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="41.4" customHeight="1">
+      <c r="A21" s="92" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="B21" s="92" t="inlineStr">
+        <is>
+          <t>Накопл.
+сделано (дн)</t>
+        </is>
+      </c>
+      <c r="C21" s="92" t="inlineStr">
+        <is>
+          <t>Общий
+объём (дн)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="110" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="110" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="110" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="110" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="110" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="110" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="110" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="110" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="110" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="110" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="102">
+        <f>SUMIFS('Дорожная карта'!$I$6:$I$16,'Дорожная карта'!$A$6:$A$16,"&lt;="&amp;A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="102">
+        <f>SUM(Бэклог!$E$5:$E$44)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -38703,7 +39648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40259,7 +41204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40556,7 +41501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41302,7 +42247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41933,7 +42878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42194,7 +43139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42608,7 +43553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43103,7 +44048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46205,6 +47150,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Оценка приоритетов по RICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="229" t="inlineStr">
+        <is>
+          <t>RICE = (Reach × Impact × Confidence) / Effort. Чем выше балл — тем выше приоритет фичи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="230" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="230" t="inlineStr">
+        <is>
+          <t>Фича / инициатива</t>
+        </is>
+      </c>
+      <c r="C4" s="230" t="inlineStr">
+        <is>
+          <t>Reach
+(польз./кв)</t>
+        </is>
+      </c>
+      <c r="D4" s="230" t="inlineStr">
+        <is>
+          <t>Impact
+(влияние)</t>
+        </is>
+      </c>
+      <c r="E4" s="230" t="inlineStr">
+        <is>
+          <t>Confidence
+(увер-ть)</t>
+        </is>
+      </c>
+      <c r="F4" s="230" t="inlineStr">
+        <is>
+          <t>Effort
+(чел-дни)</t>
+        </is>
+      </c>
+      <c r="G4" s="230" t="inlineStr">
+        <is>
+          <t>RICE
+score</t>
+        </is>
+      </c>
+      <c r="H4" s="230" t="inlineStr">
+        <is>
+          <t>Ранг</t>
+        </is>
+      </c>
+      <c r="I4" s="230" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="231" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B5" s="232" t="inlineStr">
+        <is>
+          <t>MVP оформления заказа</t>
+        </is>
+      </c>
+      <c r="C5" s="233" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D5" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="234" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" s="236">
+        <f>IFERROR(C5*D5*E5/F5,0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="234">
+        <f>IF(G5="","",RANK(G5,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I5" s="237">
+        <f>IF(G5="","",IF(G5&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G5&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="231" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="B6" s="232" t="inlineStr">
+        <is>
+          <t>Оплата картой</t>
+        </is>
+      </c>
+      <c r="C6" s="233" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="234" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="236">
+        <f>IFERROR(C6*D6*E6/F6,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="234">
+        <f>IF(G6="","",RANK(G6,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I6" s="237">
+        <f>IF(G6="","",IF(G6&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G6&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="231" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="B7" s="232" t="inlineStr">
+        <is>
+          <t>Промокоды и скидки</t>
+        </is>
+      </c>
+      <c r="C7" s="233" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="234" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="236">
+        <f>IFERROR(C7*D7*E7/F7,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="234">
+        <f>IF(G7="","",RANK(G7,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I7" s="237">
+        <f>IF(G7="","",IF(G7&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G7&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="231" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="B8" s="232" t="inlineStr">
+        <is>
+          <t>Уведомления (e-mail/push)</t>
+        </is>
+      </c>
+      <c r="C8" s="233" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D8" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F8" s="234" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" s="236">
+        <f>IFERROR(C8*D8*E8/F8,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="234">
+        <f>IF(G8="","",RANK(G8,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I8" s="237">
+        <f>IF(G8="","",IF(G8&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G8&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="231" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="B9" s="232" t="inlineStr">
+        <is>
+          <t>История заказов</t>
+        </is>
+      </c>
+      <c r="C9" s="233" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D9" s="234" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="234" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="236">
+        <f>IFERROR(C9*D9*E9/F9,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="234">
+        <f>IF(G9="","",RANK(G9,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I9" s="237">
+        <f>IF(G9="","",IF(G9&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G9&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="231" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="B10" s="232" t="inlineStr">
+        <is>
+          <t>Мобильная вёрстка</t>
+        </is>
+      </c>
+      <c r="C10" s="233" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D10" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F10" s="234" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="236">
+        <f>IFERROR(C10*D10*E10/F10,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="234">
+        <f>IF(G10="","",RANK(G10,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I10" s="237">
+        <f>IF(G10="","",IF(G10&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G10&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="231" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="B11" s="232" t="inlineStr">
+        <is>
+          <t>Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C11" s="233" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="235" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="234" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" s="236">
+        <f>IFERROR(C11*D11*E11/F11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="234">
+        <f>IF(G11="","",RANK(G11,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I11" s="237">
+        <f>IF(G11="","",IF(G11&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G11&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="231" t="inlineStr">
+        <is>
+          <t>F-08</t>
+        </is>
+      </c>
+      <c r="B12" s="232" t="inlineStr">
+        <is>
+          <t>Рекомендации товаров</t>
+        </is>
+      </c>
+      <c r="C12" s="233" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D12" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="235" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="234" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" s="236">
+        <f>IFERROR(C12*D12*E12/F12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="234">
+        <f>IF(G12="","",RANK(G12,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I12" s="237">
+        <f>IF(G12="","",IF(G12&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G12&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="231" t="inlineStr">
+        <is>
+          <t>F-09</t>
+        </is>
+      </c>
+      <c r="B13" s="232" t="inlineStr">
+        <is>
+          <t>Экспорт отчётов</t>
+        </is>
+      </c>
+      <c r="C13" s="233" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" s="234" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="235" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F13" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="236">
+        <f>IFERROR(C13*D13*E13/F13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="234">
+        <f>IF(G13="","",RANK(G13,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I13" s="237">
+        <f>IF(G13="","",IF(G13&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G13&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="231" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="B14" s="232" t="inlineStr">
+        <is>
+          <t>Мультиязычность</t>
+        </is>
+      </c>
+      <c r="C14" s="233" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D14" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="235" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="234" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="236">
+        <f>IFERROR(C14*D14*E14/F14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="234">
+        <f>IF(G14="","",RANK(G14,$G$5:$G$14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="237">
+        <f>IF(G14="","",IF(G14&gt;=0.6*MAX($G$5:$G$14),"Высокий",IF(G14&gt;=0.3*MAX($G$5:$G$14),"Средний","Низкий")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="222" t="inlineStr">
+        <is>
+          <t>Шкалы оценки</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="238" t="inlineStr">
+        <is>
+          <t>Impact (влияние на пользователя):</t>
+        </is>
+      </c>
+      <c r="B17" s="239" t="inlineStr">
+        <is>
+          <t>3 — массивное · 2 — высокое · 1 — среднее · 0.5 — низкое · 0.25 — минимальное</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="238" t="inlineStr">
+        <is>
+          <t>Confidence (уверенность в оценке):</t>
+        </is>
+      </c>
+      <c r="B18" s="239" t="inlineStr">
+        <is>
+          <t>100% — высокая · 80% — средняя · 50% — низкая</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="238" t="inlineStr">
+        <is>
+          <t>Reach:</t>
+        </is>
+      </c>
+      <c r="B19" s="239" t="inlineStr">
+        <is>
+          <t>сколько пользователей затронет фича за квартал</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="238" t="inlineStr">
+        <is>
+          <t>Effort:</t>
+        </is>
+      </c>
+      <c r="B20" s="239" t="inlineStr">
+        <is>
+          <t>суммарные трудозатраты команды, человеко-дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="238" t="inlineStr">
+        <is>
+          <t>Приоритет:</t>
+        </is>
+      </c>
+      <c r="B21" s="239" t="inlineStr">
+        <is>
+          <t>Высокий ≥ 60% макс. балла · Средний ≥ 30% · иначе Низкий</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I5:I14">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="39">
+      <formula>"Высокий"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="40">
+      <formula>"Средний"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="41">
+      <formula>"Низкий"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G14">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"3,2,1,0.5,0.25"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,0.8,0.5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -46662,7 +48157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46998,7 +48493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47300,769 +48795,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="16.6640625" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10.77734375" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="198" t="inlineStr">
-        <is>
-          <t>Технический долг</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="199" t="inlineStr">
-        <is>
-          <t>Реестр техдолга: область, тип, влияние, оценка, план спринта, статус.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="41.4" customHeight="1">
-      <c r="A4" s="200" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="200" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="C4" s="200" t="inlineStr">
-        <is>
-          <t>Область</t>
-        </is>
-      </c>
-      <c r="D4" s="200" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="E4" s="200" t="inlineStr">
-        <is>
-          <t>Влияние</t>
-        </is>
-      </c>
-      <c r="F4" s="200" t="inlineStr">
-        <is>
-          <t>Оценка (дн)</t>
-        </is>
-      </c>
-      <c r="G4" s="200" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="H4" s="200" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="I4" s="200" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="J4" s="200" t="inlineStr">
-        <is>
-          <t>Спринт
-создан</t>
-        </is>
-      </c>
-      <c r="K4" s="200" t="inlineStr">
-        <is>
-          <t>Спринт
-погашен</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="27.6" customHeight="1">
-      <c r="A5" s="201" t="inlineStr">
-        <is>
-          <t>TD-1</t>
-        </is>
-      </c>
-      <c r="B5" s="202" t="inlineStr">
-        <is>
-          <t>Рефакторинг модуля авторизации</t>
-        </is>
-      </c>
-      <c r="C5" s="201" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="D5" s="201" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="E5" s="201" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="210" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="201" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" s="201" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="201" t="inlineStr">
-        <is>
-          <t>Закрыт</t>
-        </is>
-      </c>
-      <c r="J5" s="212" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="212" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="27.6" customHeight="1">
-      <c r="A6" s="201" t="inlineStr">
-        <is>
-          <t>TD-2</t>
-        </is>
-      </c>
-      <c r="B6" s="202" t="inlineStr">
-        <is>
-          <t>Автотесты оформления заказа</t>
-        </is>
-      </c>
-      <c r="C6" s="201" t="inlineStr">
-        <is>
-          <t>Checkout</t>
-        </is>
-      </c>
-      <c r="D6" s="201" t="inlineStr">
-        <is>
-          <t>Тесты</t>
-        </is>
-      </c>
-      <c r="E6" s="201" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="201" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H6" s="201" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="201" t="inlineStr">
-        <is>
-          <t>Закрыт</t>
-        </is>
-      </c>
-      <c r="J6" s="212" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="212" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="201" t="inlineStr">
-        <is>
-          <t>TD-3</t>
-        </is>
-      </c>
-      <c r="B7" s="202" t="inlineStr">
-        <is>
-          <t>Убрать дубли в API заказов</t>
-        </is>
-      </c>
-      <c r="C7" s="201" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="D7" s="201" t="inlineStr">
-        <is>
-          <t>Архитектура</t>
-        </is>
-      </c>
-      <c r="E7" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" s="210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H7" s="201" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="201" t="inlineStr">
-        <is>
-          <t>Открыт</t>
-        </is>
-      </c>
-      <c r="J7" s="212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="212" t="n"/>
-    </row>
-    <row r="8" ht="27.6" customHeight="1">
-      <c r="A8" s="201" t="inlineStr">
-        <is>
-          <t>TD-4</t>
-        </is>
-      </c>
-      <c r="B8" s="202" t="inlineStr">
-        <is>
-          <t>Обновить документацию API</t>
-        </is>
-      </c>
-      <c r="C8" s="201" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D8" s="201" t="inlineStr">
-        <is>
-          <t>Документация</t>
-        </is>
-      </c>
-      <c r="E8" s="201" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F8" s="210" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="201" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H8" s="201" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="201" t="inlineStr">
-        <is>
-          <t>Открыт</t>
-        </is>
-      </c>
-      <c r="J8" s="212" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="212" t="n"/>
-    </row>
-    <row r="9" ht="27.6" customHeight="1">
-      <c r="A9" s="201" t="inlineStr">
-        <is>
-          <t>TD-5</t>
-        </is>
-      </c>
-      <c r="B9" s="202" t="inlineStr">
-        <is>
-          <t>Мониторинг и алерты платежей</t>
-        </is>
-      </c>
-      <c r="C9" s="201" t="inlineStr">
-        <is>
-          <t>Payments</t>
-        </is>
-      </c>
-      <c r="D9" s="201" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E9" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F9" s="210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H9" s="201" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="201" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="J9" s="212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="212" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="201" t="inlineStr">
-        <is>
-          <t>TD-6</t>
-        </is>
-      </c>
-      <c r="B10" s="202" t="inlineStr">
-        <is>
-          <t>Оптимизация запросов БД</t>
-        </is>
-      </c>
-      <c r="C10" s="201" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="D10" s="201" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="E10" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F10" s="210" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="201" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H10" s="201" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="201" t="inlineStr">
-        <is>
-          <t>Открыт</t>
-        </is>
-      </c>
-      <c r="J10" s="212" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="212" t="n"/>
-    </row>
-    <row r="12" ht="15.6" customHeight="1">
-      <c r="A12" s="207" t="inlineStr">
-        <is>
-          <t>По типу</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="200" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="B13" s="200" t="inlineStr">
-        <is>
-          <t>Оценка (дн)</t>
-        </is>
-      </c>
-      <c r="C13" s="200" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="27.6" customHeight="1">
-      <c r="A14" s="208" t="inlineStr">
-        <is>
-          <t>Архитектура</t>
-        </is>
-      </c>
-      <c r="B14" s="206">
-        <f>SUMIF($D$5:$D$10,A14,$F$5:$F$10)</f>
-        <v/>
-      </c>
-      <c r="C14" s="205">
-        <f>COUNTIF($D$5:$D$10,A14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="208" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B15" s="206">
-        <f>SUMIF($D$5:$D$10,A15,$F$5:$F$10)</f>
-        <v/>
-      </c>
-      <c r="C15" s="205">
-        <f>COUNTIF($D$5:$D$10,A15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="208" t="inlineStr">
-        <is>
-          <t>Тесты</t>
-        </is>
-      </c>
-      <c r="B16" s="206">
-        <f>SUMIF($D$5:$D$10,A16,$F$5:$F$10)</f>
-        <v/>
-      </c>
-      <c r="C16" s="205">
-        <f>COUNTIF($D$5:$D$10,A16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="208" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="B17" s="206">
-        <f>SUMIF($D$5:$D$10,A17,$F$5:$F$10)</f>
-        <v/>
-      </c>
-      <c r="C17" s="205">
-        <f>COUNTIF($D$5:$D$10,A17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="208" t="inlineStr">
-        <is>
-          <t>Документация</t>
-        </is>
-      </c>
-      <c r="B18" s="206">
-        <f>SUMIF($D$5:$D$10,A18,$F$5:$F$10)</f>
-        <v/>
-      </c>
-      <c r="C18" s="205">
-        <f>COUNTIF($D$5:$D$10,A18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15.6" customHeight="1">
-      <c r="A20" s="207" t="inlineStr">
-        <is>
-          <t>По статусу</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="200" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="B21" s="200" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="208" t="inlineStr">
-        <is>
-          <t>Открыт</t>
-        </is>
-      </c>
-      <c r="B22" s="205">
-        <f>COUNTIF($I$5:$I$10,A22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="208" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="B23" s="205">
-        <f>COUNTIF($I$5:$I$10,A23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="208" t="inlineStr">
-        <is>
-          <t>Закрыт</t>
-        </is>
-      </c>
-      <c r="B24" s="205">
-        <f>COUNTIF($I$5:$I$10,A24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15.6" customHeight="1">
-      <c r="A27" s="207" t="inlineStr">
-        <is>
-          <t>Тренд техдолга (создано / погашено по спринтам)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="27.6" customHeight="1">
-      <c r="A28" s="200" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="B28" s="200" t="inlineStr">
-        <is>
-          <t>Создано</t>
-        </is>
-      </c>
-      <c r="C28" s="200" t="inlineStr">
-        <is>
-          <t>Погашено</t>
-        </is>
-      </c>
-      <c r="D28" s="200" t="inlineStr">
-        <is>
-          <t>Открыто (накопит.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="208" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="205">
-        <f>COUNTIF($J$5:$J$10,A29)</f>
-        <v/>
-      </c>
-      <c r="C29" s="205">
-        <f>COUNTIF($K$5:$K$10,A29)</f>
-        <v/>
-      </c>
-      <c r="D29" s="209">
-        <f>B29-C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="208" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="205">
-        <f>COUNTIF($J$5:$J$10,A30)</f>
-        <v/>
-      </c>
-      <c r="C30" s="205">
-        <f>COUNTIF($K$5:$K$10,A30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="209">
-        <f>D29+B30-C30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="208" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="205">
-        <f>COUNTIF($J$5:$J$10,A31)</f>
-        <v/>
-      </c>
-      <c r="C31" s="205">
-        <f>COUNTIF($K$5:$K$10,A31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="209">
-        <f>D30+B31-C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="208" t="n">
-        <v>4</v>
-      </c>
-      <c r="B32" s="205">
-        <f>COUNTIF($J$5:$J$10,A32)</f>
-        <v/>
-      </c>
-      <c r="C32" s="205">
-        <f>COUNTIF($K$5:$K$10,A32)</f>
-        <v/>
-      </c>
-      <c r="D32" s="209">
-        <f>D31+B32-C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="208" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="205">
-        <f>COUNTIF($J$5:$J$10,A33)</f>
-        <v/>
-      </c>
-      <c r="C33" s="205">
-        <f>COUNTIF($K$5:$K$10,A33)</f>
-        <v/>
-      </c>
-      <c r="D33" s="209">
-        <f>D32+B33-C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="208" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="205">
-        <f>COUNTIF($J$5:$J$10,A34)</f>
-        <v/>
-      </c>
-      <c r="C34" s="205">
-        <f>COUNTIF($K$5:$K$10,A34)</f>
-        <v/>
-      </c>
-      <c r="D34" s="209">
-        <f>D33+B34-C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="208" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="205">
-        <f>COUNTIF($J$5:$J$10,A35)</f>
-        <v/>
-      </c>
-      <c r="C35" s="205">
-        <f>COUNTIF($K$5:$K$10,A35)</f>
-        <v/>
-      </c>
-      <c r="D35" s="209">
-        <f>D34+B35-C35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="208" t="n">
-        <v>8</v>
-      </c>
-      <c r="B36" s="205">
-        <f>COUNTIF($J$5:$J$10,A36)</f>
-        <v/>
-      </c>
-      <c r="C36" s="205">
-        <f>COUNTIF($K$5:$K$10,A36)</f>
-        <v/>
-      </c>
-      <c r="D36" s="209">
-        <f>D35+B36-C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="208" t="n">
-        <v>9</v>
-      </c>
-      <c r="B37" s="205">
-        <f>COUNTIF($J$5:$J$10,A37)</f>
-        <v/>
-      </c>
-      <c r="C37" s="205">
-        <f>COUNTIF($K$5:$K$10,A37)</f>
-        <v/>
-      </c>
-      <c r="D37" s="209">
-        <f>D36+B37-C37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="208" t="n">
-        <v>10</v>
-      </c>
-      <c r="B38" s="205">
-        <f>COUNTIF($J$5:$J$10,A38)</f>
-        <v/>
-      </c>
-      <c r="C38" s="205">
-        <f>COUNTIF($K$5:$K$10,A38)</f>
-        <v/>
-      </c>
-      <c r="D38" s="209">
-        <f>D37+B38-C38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="208" t="n">
-        <v>11</v>
-      </c>
-      <c r="B39" s="205">
-        <f>COUNTIF($J$5:$J$10,A39)</f>
-        <v/>
-      </c>
-      <c r="C39" s="205">
-        <f>COUNTIF($K$5:$K$10,A39)</f>
-        <v/>
-      </c>
-      <c r="D39" s="209">
-        <f>D38+B39-C39</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Архитектура,Код,Тесты,Инфраструктура,Документация"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I5 I6 I7 I8 I9 I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Открыт,В работе,Закрыт"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Планирование_спринта_PRO.xlsx
+++ b/Планирование_спринта_PRO.xlsx
@@ -21,20 +21,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OKR" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ёмкость на горизонт" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гант" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Капасити" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Календарь" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Загрузка по ролям" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бэклог" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сгорание" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Качество" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баги" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFD" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Метрики и прогноз" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cycle time" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Риски" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица рисков" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Зависимости" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Капасити" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Календарь" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Загрузка по ролям" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бэклог" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сгорание" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Качество" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баги" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CFD" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Метрики и прогноз" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cycle time" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Риски" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица рисков" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time to Market" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -875,7 +876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1450,6 +1451,19 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -17114,6 +17128,87 @@
       <tx>
         <rich>
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Зависимости по статусам</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Зависимости'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Зависимости'!$A$16:$A$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Зависимости'!$B$16:$B$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
@@ -17405,7 +17500,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -17779,7 +17874,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18163,7 +18258,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18521,7 +18616,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -18816,194 +18911,6 @@
       <legendPos val="b"/>
       <overlay val="0"/>
     </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>% закрытых по спринтам</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="1"/>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Баги!$N$5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>% закрытых</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="1"/>
-          <cat>
-            <numRef>
-              <f>Баги!$J$6:$J$16</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Баги!$N$6:$N$16</f>
-              <numCache>
-                <formatCode>0%</formatCode>
-                <ptCount val="11"/>
-                <pt idx="0">
-                  <v>0.8</v>
-                </pt>
-                <pt idx="1">
-                  <v>1</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="100"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="10"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -19288,6 +19195,194 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
+              <a:t>% закрытых по спринтам</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Баги!$N$5</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>% закрытых</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <numRef>
+              <f>Баги!$J$6:$J$16</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>5</v>
+                </pt>
+                <pt idx="5">
+                  <v>6</v>
+                </pt>
+                <pt idx="6">
+                  <v>7</v>
+                </pt>
+                <pt idx="7">
+                  <v>8</v>
+                </pt>
+                <pt idx="8">
+                  <v>9</v>
+                </pt>
+                <pt idx="9">
+                  <v>10</v>
+                </pt>
+                <pt idx="10">
+                  <v>11</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Баги!$N$6:$N$16</f>
+              <numCache>
+                <formatCode>0%</formatCode>
+                <ptCount val="11"/>
+                <pt idx="0">
+                  <v>0.8</v>
+                </pt>
+                <pt idx="1">
+                  <v>1</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Доля багов по спринтам</a:t>
             </a:r>
           </a:p>
@@ -19430,7 +19525,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -19891,7 +19986,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart63.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20088,7 +20183,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart64.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20280,7 +20375,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart65.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20532,7 +20627,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart66.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -20784,7 +20879,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart67.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -21103,7 +21198,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart68.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -21868,7 +21963,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart69.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -22069,151 +22164,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart69.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Риски по баллу (Вероятность × Влияние)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Матрица рисков'!$E$4</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Балл</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C00000"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="1"/>
-          <cat>
-            <strRef>
-              <f>'Матрица рисков'!$B$5:$B$8</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Зависимость от внешнего API оплаты</v>
-                </pt>
-                <pt idx="1">
-                  <v>Отпуска в декабре (Спринт 11)</v>
-                </pt>
-                <pt idx="2">
-                  <v>Недооценка интеграции</v>
-                </pt>
-                <pt idx="3">
-                  <v>Текучесть в QA</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Матрица рисков'!$E$5:$E$8</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>20</v>
-                </pt>
-                <pt idx="1">
-                  <v>15</v>
-                </pt>
-                <pt idx="2">
-                  <v>12</v>
-                </pt>
-                <pt idx="3">
-                  <v>8</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="100"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="1"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <majorGridlines/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="10"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -22355,6 +22305,151 @@
 </file>
 
 <file path=xl/charts/chart70.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Риски по баллу (Вероятность × Влияние)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Матрица рисков'!$E$4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Балл</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="1"/>
+          <cat>
+            <strRef>
+              <f>'Матрица рисков'!$B$5:$B$8</f>
+              <strCache>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>Зависимость от внешнего API оплаты</v>
+                </pt>
+                <pt idx="1">
+                  <v>Отпуска в декабре (Спринт 11)</v>
+                </pt>
+                <pt idx="2">
+                  <v>Недооценка интеграции</v>
+                </pt>
+                <pt idx="3">
+                  <v>Текучесть в QA</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Матрица рисков'!$E$5:$E$8</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>20</v>
+                </pt>
+                <pt idx="1">
+                  <v>15</v>
+                </pt>
+                <pt idx="2">
+                  <v>12</v>
+                </pt>
+                <pt idx="3">
+                  <v>8</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart71.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -22587,7 +22682,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart72.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -24663,6 +24758,33 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>8</col>
       <colOff>274320</colOff>
       <row>5</row>
@@ -24686,7 +24808,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24735,7 +24857,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24762,7 +24884,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24833,7 +24955,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24860,7 +24982,56 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>106680</colOff>
+      <row>19</row>
+      <rowOff>160020</rowOff>
+    </from>
+    <ext cx="6120000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -24975,56 +25146,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6120000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>106680</colOff>
-      <row>19</row>
-      <rowOff>160020</rowOff>
-    </from>
-    <ext cx="6120000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25051,7 +25173,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25078,7 +25200,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25135,7 +25257,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -25162,7 +25284,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -28018,7 +28140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -28029,6 +28151,7 @@
     <col width="12" customWidth="1" min="6" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" customHeight="1">
@@ -28097,6 +28220,12 @@
 путь</t>
         </is>
       </c>
+      <c r="K4" s="230" t="inlineStr">
+        <is>
+          <t>Внешняя
+зависимость</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="119">
@@ -28137,6 +28266,10 @@
           <t>Да</t>
         </is>
       </c>
+      <c r="K5" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A5)=0,"","◆ "&amp;IFERROR(VLOOKUP(A5,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A5,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="119">
@@ -28177,6 +28310,10 @@
         <v/>
       </c>
       <c r="J6" s="140" t="n"/>
+      <c r="K6" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A6)=0,"","◆ "&amp;IFERROR(VLOOKUP(A6,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A6,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="119">
@@ -28213,6 +28350,10 @@
         <v/>
       </c>
       <c r="J7" s="140" t="n"/>
+      <c r="K7" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A7)=0,"","◆ "&amp;IFERROR(VLOOKUP(A7,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A7,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="119">
@@ -28249,6 +28390,10 @@
         <v/>
       </c>
       <c r="J8" s="140" t="n"/>
+      <c r="K8" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A8)=0,"","◆ "&amp;IFERROR(VLOOKUP(A8,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A8,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="119">
@@ -28293,6 +28438,10 @@
           <t>Да</t>
         </is>
       </c>
+      <c r="K9" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A9)=0,"","◆ "&amp;IFERROR(VLOOKUP(A9,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A9,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="119">
@@ -28329,6 +28478,10 @@
         <v/>
       </c>
       <c r="J10" s="140" t="n"/>
+      <c r="K10" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A10)=0,"","◆ "&amp;IFERROR(VLOOKUP(A10,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A10,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="119">
@@ -28365,6 +28518,10 @@
         <v/>
       </c>
       <c r="J11" s="140" t="n"/>
+      <c r="K11" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A11)=0,"","◆ "&amp;IFERROR(VLOOKUP(A11,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A11,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="119">
@@ -28401,6 +28558,10 @@
         <v/>
       </c>
       <c r="J12" s="140" t="n"/>
+      <c r="K12" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A12)=0,"","◆ "&amp;IFERROR(VLOOKUP(A12,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A12,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="119">
@@ -28437,6 +28598,10 @@
         <v/>
       </c>
       <c r="J13" s="140" t="n"/>
+      <c r="K13" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A13)=0,"","◆ "&amp;IFERROR(VLOOKUP(A13,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A13,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="119">
@@ -28473,6 +28638,10 @@
         <v/>
       </c>
       <c r="J14" s="140" t="n"/>
+      <c r="K14" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A14)=0,"","◆ "&amp;IFERROR(VLOOKUP(A14,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A14,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="119">
@@ -28509,6 +28678,10 @@
         <v/>
       </c>
       <c r="J15" s="140" t="n"/>
+      <c r="K15" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A15)=0,"","◆ "&amp;IFERROR(VLOOKUP(A15,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A15,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="119">
@@ -28549,6 +28722,10 @@
         <v/>
       </c>
       <c r="J16" s="140" t="n"/>
+      <c r="K16" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A16)=0,"","◆ "&amp;IFERROR(VLOOKUP(A16,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A16,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="119">
@@ -28593,6 +28770,10 @@
           <t>Да</t>
         </is>
       </c>
+      <c r="K17" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A17)=0,"","◆ "&amp;IFERROR(VLOOKUP(A17,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A17,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="119">
@@ -28637,6 +28818,10 @@
           <t>Да</t>
         </is>
       </c>
+      <c r="K18" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A18)=0,"","◆ "&amp;IFERROR(VLOOKUP(A18,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A18,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="119">
@@ -28673,6 +28858,10 @@
         <v/>
       </c>
       <c r="J19" s="140" t="n"/>
+      <c r="K19" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A19)=0,"","◆ "&amp;IFERROR(VLOOKUP(A19,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A19,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="119">
@@ -28713,6 +28902,10 @@
         <v/>
       </c>
       <c r="J20" s="140" t="n"/>
+      <c r="K20" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A20)=0,"","◆ "&amp;IFERROR(VLOOKUP(A20,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A20,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="119">
@@ -28753,6 +28946,10 @@
         <v/>
       </c>
       <c r="J21" s="140" t="n"/>
+      <c r="K21" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A21)=0,"","◆ "&amp;IFERROR(VLOOKUP(A21,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A21,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="119">
@@ -28789,6 +28986,10 @@
         <v/>
       </c>
       <c r="J22" s="140" t="n"/>
+      <c r="K22" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A22)=0,"","◆ "&amp;IFERROR(VLOOKUP(A22,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A22,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="27.6" customHeight="1">
       <c r="A23" s="119">
@@ -28825,6 +29026,10 @@
         <v/>
       </c>
       <c r="J23" s="140" t="n"/>
+      <c r="K23" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A23)=0,"","◆ "&amp;IFERROR(VLOOKUP(A23,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A23,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="119">
@@ -28861,6 +29066,10 @@
         <v/>
       </c>
       <c r="J24" s="140" t="n"/>
+      <c r="K24" s="240">
+        <f>IF(COUNTIF(Зависимости!$D$5:$D$100,A24)=0,"","◆ "&amp;IFERROR(VLOOKUP(A24,Зависимости!$D$5:$I$100,2,FALSE),"")&amp;" · "&amp;IFERROR(VLOOKUP(A24,Зависимости!$D$5:$I$100,6,FALSE),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="119">
@@ -29763,6 +29972,639 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Зависимости от других стримов</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="229" t="inlineStr">
+        <is>
+          <t>Межстримовые зависимости задач, историй и фич. Направление, статус (RAG) и риск.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="230" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="230" t="inlineStr">
+        <is>
+          <t>Элемент</t>
+        </is>
+      </c>
+      <c r="C4" s="230" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D4" s="230" t="inlineStr">
+        <is>
+          <t>Задача
+(Гант)</t>
+        </is>
+      </c>
+      <c r="E4" s="230" t="inlineStr">
+        <is>
+          <t>Внешний стрим</t>
+        </is>
+      </c>
+      <c r="F4" s="230" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="G4" s="230" t="inlineStr">
+        <is>
+          <t>Что именно</t>
+        </is>
+      </c>
+      <c r="H4" s="230" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="I4" s="230" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="J4" s="230" t="inlineStr">
+        <is>
+          <t>Владелец</t>
+        </is>
+      </c>
+      <c r="K4" s="230" t="inlineStr">
+        <is>
+          <t>Риск</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="241" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="B5" s="242" t="inlineStr">
+        <is>
+          <t>Интеграция платежей</t>
+        </is>
+      </c>
+      <c r="C5" s="234" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="D5" s="234" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="E5" s="242" t="inlineStr">
+        <is>
+          <t>Платёжный шлюз</t>
+        </is>
+      </c>
+      <c r="F5" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G5" s="242" t="inlineStr">
+        <is>
+          <t>API оплаты v2 (токенизация карт)</t>
+        </is>
+      </c>
+      <c r="H5" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="243" t="inlineStr">
+        <is>
+          <t>Заблокировано</t>
+        </is>
+      </c>
+      <c r="J5" s="243" t="inlineStr">
+        <is>
+          <t>Команда Payments</t>
+        </is>
+      </c>
+      <c r="K5" s="234" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="241" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="B6" s="242" t="inlineStr">
+        <is>
+          <t>Оплата картой</t>
+        </is>
+      </c>
+      <c r="C6" s="234" t="inlineStr">
+        <is>
+          <t>Фича</t>
+        </is>
+      </c>
+      <c r="D6" s="234" t="inlineStr"/>
+      <c r="E6" s="242" t="inlineStr">
+        <is>
+          <t>Платёжный шлюз</t>
+        </is>
+      </c>
+      <c r="F6" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G6" s="242" t="inlineStr">
+        <is>
+          <t>Сертификация PCI DSS</t>
+        </is>
+      </c>
+      <c r="H6" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="243" t="inlineStr">
+        <is>
+          <t>Ожидается</t>
+        </is>
+      </c>
+      <c r="J6" s="243" t="inlineStr">
+        <is>
+          <t>Security / Payments</t>
+        </is>
+      </c>
+      <c r="K6" s="234" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="241" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="B7" s="242" t="inlineStr">
+        <is>
+          <t>Уведомления (e-mail/push)</t>
+        </is>
+      </c>
+      <c r="C7" s="234" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="D7" s="234" t="inlineStr">
+        <is>
+          <t>T-08</t>
+        </is>
+      </c>
+      <c r="E7" s="242" t="inlineStr">
+        <is>
+          <t>Инфраструктура / DevOps</t>
+        </is>
+      </c>
+      <c r="F7" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G7" s="242" t="inlineStr">
+        <is>
+          <t>Сервис рассылок (SMTP + Push)</t>
+        </is>
+      </c>
+      <c r="H7" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="243" t="inlineStr">
+        <is>
+          <t>Подтверждено</t>
+        </is>
+      </c>
+      <c r="J7" s="243" t="inlineStr">
+        <is>
+          <t>Platform Team</t>
+        </is>
+      </c>
+      <c r="K7" s="234" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="241" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="B8" s="242" t="inlineStr">
+        <is>
+          <t>API промокодов</t>
+        </is>
+      </c>
+      <c r="C8" s="234" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="D8" s="234" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+      <c r="E8" s="242" t="inlineStr">
+        <is>
+          <t>Каталог / Контент</t>
+        </is>
+      </c>
+      <c r="F8" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G8" s="242" t="inlineStr">
+        <is>
+          <t>Каталог товаров и цен</t>
+        </is>
+      </c>
+      <c r="H8" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="243" t="inlineStr">
+        <is>
+          <t>Получено</t>
+        </is>
+      </c>
+      <c r="J8" s="243" t="inlineStr">
+        <is>
+          <t>Catalog Team</t>
+        </is>
+      </c>
+      <c r="K8" s="234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="241" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="B9" s="242" t="inlineStr">
+        <is>
+          <t>Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C9" s="234" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+      <c r="D9" s="234" t="inlineStr"/>
+      <c r="E9" s="242" t="inlineStr">
+        <is>
+          <t>Идентификация (SSO)</t>
+        </is>
+      </c>
+      <c r="F9" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G9" s="242" t="inlineStr">
+        <is>
+          <t>Единый вход (OAuth2/OIDC)</t>
+        </is>
+      </c>
+      <c r="H9" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="243" t="inlineStr">
+        <is>
+          <t>Ожидается</t>
+        </is>
+      </c>
+      <c r="J9" s="243" t="inlineStr">
+        <is>
+          <t>IAM Team</t>
+        </is>
+      </c>
+      <c r="K9" s="234" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="241" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="B10" s="242" t="inlineStr">
+        <is>
+          <t>Экран корзины</t>
+        </is>
+      </c>
+      <c r="C10" s="234" t="inlineStr">
+        <is>
+          <t>Фича</t>
+        </is>
+      </c>
+      <c r="D10" s="234" t="inlineStr">
+        <is>
+          <t>T-02</t>
+        </is>
+      </c>
+      <c r="E10" s="242" t="inlineStr">
+        <is>
+          <t>Мобильное приложение</t>
+        </is>
+      </c>
+      <c r="F10" s="243" t="inlineStr">
+        <is>
+          <t>Зависят от нас</t>
+        </is>
+      </c>
+      <c r="G10" s="242" t="inlineStr">
+        <is>
+          <t>REST API заказов для мобильного клиента</t>
+        </is>
+      </c>
+      <c r="H10" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="243" t="inlineStr">
+        <is>
+          <t>Подтверждено</t>
+        </is>
+      </c>
+      <c r="J10" s="243" t="inlineStr">
+        <is>
+          <t>Mobile Team</t>
+        </is>
+      </c>
+      <c r="K10" s="234" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="241" t="inlineStr">
+        <is>
+          <t>D-07</t>
+        </is>
+      </c>
+      <c r="B11" s="242" t="inlineStr">
+        <is>
+          <t>Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="C11" s="234" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="D11" s="234" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="E11" s="242" t="inlineStr">
+        <is>
+          <t>Data Platform / Аналитика</t>
+        </is>
+      </c>
+      <c r="F11" s="243" t="inlineStr">
+        <is>
+          <t>Мы зависим</t>
+        </is>
+      </c>
+      <c r="G11" s="242" t="inlineStr">
+        <is>
+          <t>Шина событий (Kafka topics)</t>
+        </is>
+      </c>
+      <c r="H11" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="243" t="inlineStr">
+        <is>
+          <t>Заблокировано</t>
+        </is>
+      </c>
+      <c r="J11" s="243" t="inlineStr">
+        <is>
+          <t>Data Platform</t>
+        </is>
+      </c>
+      <c r="K11" s="234" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="241" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="B12" s="242" t="inlineStr">
+        <is>
+          <t>Экспорт отчётов</t>
+        </is>
+      </c>
+      <c r="C12" s="234" t="inlineStr">
+        <is>
+          <t>Фича</t>
+        </is>
+      </c>
+      <c r="D12" s="234" t="inlineStr"/>
+      <c r="E12" s="242" t="inlineStr">
+        <is>
+          <t>Data Platform / Аналитика</t>
+        </is>
+      </c>
+      <c r="F12" s="243" t="inlineStr">
+        <is>
+          <t>Зависят от нас</t>
+        </is>
+      </c>
+      <c r="G12" s="242" t="inlineStr">
+        <is>
+          <t>Витрина заказов для BI</t>
+        </is>
+      </c>
+      <c r="H12" s="234" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="243" t="inlineStr">
+        <is>
+          <t>Ожидается</t>
+        </is>
+      </c>
+      <c r="J12" s="243" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="K12" s="234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="222" t="inlineStr">
+        <is>
+          <t>Сводка по статусам</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="244" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="B15" s="244" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="186" t="inlineStr">
+        <is>
+          <t>Ожидается</t>
+        </is>
+      </c>
+      <c r="B16" s="186">
+        <f>COUNTIF($I$5:$I$12,A16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="186" t="inlineStr">
+        <is>
+          <t>Подтверждено</t>
+        </is>
+      </c>
+      <c r="B17" s="186">
+        <f>COUNTIF($I$5:$I$12,A17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="186" t="inlineStr">
+        <is>
+          <t>Получено</t>
+        </is>
+      </c>
+      <c r="B18" s="186">
+        <f>COUNTIF($I$5:$I$12,A18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="186" t="inlineStr">
+        <is>
+          <t>Заблокировано</t>
+        </is>
+      </c>
+      <c r="B19" s="186">
+        <f>COUNTIF($I$5:$I$12,A19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="186" t="inlineStr">
+        <is>
+          <t>Просрочено</t>
+        </is>
+      </c>
+      <c r="B20" s="186">
+        <f>COUNTIF($I$5:$I$12,A20)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I5:I12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="41">
+      <formula>"Заблокировано"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="41">
+      <formula>"Просрочено"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="40">
+      <formula>"Ожидается"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="39">
+      <formula>"Получено"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="39">
+      <formula>"Подтверждено"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="C5:C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"История,Задача,Фича,Эпик"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Мы зависим,Зависят от нас"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Ожидается,Подтверждено,Получено,Заблокировано,Просрочено"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K5:K12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34664,7 +35506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34826,7 +35668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35480,2756 +36322,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="15.88671875" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="17"/>
-    <col width="8" customWidth="1" min="18" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Бэклог спринта (задачи)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Оценка (дн) — трудоёмкость задачи в человеко-днях. Остаток пересчитывается по статусу («Готово» → 0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27.6" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Оценка (дн)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Остаток (дн)</t>
-        </is>
-      </c>
-      <c r="H4" s="39" t="inlineStr">
-        <is>
-          <t>Роль</t>
-        </is>
-      </c>
-      <c r="I4" s="39" t="inlineStr">
-        <is>
-          <t>Факт (дн)</t>
-        </is>
-      </c>
-      <c r="J4" s="39" t="inlineStr">
-        <is>
-          <t>Точность
-(Факт/Оценка)</t>
-        </is>
-      </c>
-      <c r="K4" s="39" t="inlineStr">
-        <is>
-          <t>Блокер</t>
-        </is>
-      </c>
-      <c r="L4" s="39" t="inlineStr">
-        <is>
-          <t>Дней
-в блоке</t>
-        </is>
-      </c>
-      <c r="M4" s="113" t="inlineStr">
-        <is>
-          <t>Спринт</t>
-        </is>
-      </c>
-      <c r="N4" s="92" t="inlineStr">
-        <is>
-          <t>Добавлено
-после старта</t>
-        </is>
-      </c>
-      <c r="O4" s="92" t="inlineStr">
-        <is>
-          <t>Создана</t>
-        </is>
-      </c>
-      <c r="P4" s="92" t="inlineStr">
-        <is>
-          <t>В работу</t>
-        </is>
-      </c>
-      <c r="Q4" s="92" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="R4" s="92" t="inlineStr">
-        <is>
-          <t>Cycle
-(дн)</t>
-        </is>
-      </c>
-      <c r="S4" s="92" t="inlineStr">
-        <is>
-          <t>Lead
-(дн)</t>
-        </is>
-      </c>
-      <c r="T4" s="92" t="inlineStr">
-        <is>
-          <t>Возраст
-WIP (дн)</t>
-        </is>
-      </c>
-      <c r="U4" s="200" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="94" t="inlineStr">
-        <is>
-          <t>T-01</t>
-        </is>
-      </c>
-      <c r="B5" s="95" t="inlineStr">
-        <is>
-          <t>Проектирование API заказов</t>
-        </is>
-      </c>
-      <c r="C5" s="95" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="D5" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G5" s="23">
-        <f>IF(F5="Готово",0,IF(E5="","",E5))</f>
-        <v/>
-      </c>
-      <c r="H5" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C5,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="97" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="72">
-        <f>IF(AND(I5&lt;&gt;"",E5&lt;&gt;""),I5/E5,"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L5" s="33" t="n"/>
-      <c r="M5" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O5" s="128" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P5" s="128" t="n">
-        <v>46237</v>
-      </c>
-      <c r="Q5" s="128" t="n">
-        <v>46240</v>
-      </c>
-      <c r="R5" s="90">
-        <f>IF(AND(Q5&lt;&gt;"",P5&lt;&gt;""),Q5-P5,"")</f>
-        <v/>
-      </c>
-      <c r="S5" s="90">
-        <f>IF(AND(Q5&lt;&gt;"",O5&lt;&gt;""),Q5-O5,"")</f>
-        <v/>
-      </c>
-      <c r="T5" s="90">
-        <f>IF(AND(F5="В работе",P5&lt;&gt;""),Параметры!$B$10-P5,"")</f>
-        <v/>
-      </c>
-      <c r="U5" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="94" t="inlineStr">
-        <is>
-          <t>T-02</t>
-        </is>
-      </c>
-      <c r="B6" s="95" t="inlineStr">
-        <is>
-          <t>Экран корзины (вёрстка)</t>
-        </is>
-      </c>
-      <c r="C6" s="95" t="inlineStr">
-        <is>
-          <t>Петрова М.</t>
-        </is>
-      </c>
-      <c r="D6" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="96" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G6" s="23">
-        <f>IF(F6="Готово",0,IF(E6="","",E6))</f>
-        <v/>
-      </c>
-      <c r="H6" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C6,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="97" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="72">
-        <f>IF(AND(I6&lt;&gt;"",E6&lt;&gt;""),I6/E6,"")</f>
-        <v/>
-      </c>
-      <c r="K6" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L6" s="33" t="n"/>
-      <c r="M6" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O6" s="128" t="n">
-        <v>46233</v>
-      </c>
-      <c r="P6" s="128" t="n">
-        <v>46238</v>
-      </c>
-      <c r="Q6" s="128" t="n">
-        <v>46246</v>
-      </c>
-      <c r="R6" s="90">
-        <f>IF(AND(Q6&lt;&gt;"",P6&lt;&gt;""),Q6-P6,"")</f>
-        <v/>
-      </c>
-      <c r="S6" s="90">
-        <f>IF(AND(Q6&lt;&gt;"",O6&lt;&gt;""),Q6-O6,"")</f>
-        <v/>
-      </c>
-      <c r="T6" s="90">
-        <f>IF(AND(F6="В работе",P6&lt;&gt;""),Параметры!$B$10-P6,"")</f>
-        <v/>
-      </c>
-      <c r="U6" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="94" t="inlineStr">
-        <is>
-          <t>T-09</t>
-        </is>
-      </c>
-      <c r="B7" s="95" t="inlineStr">
-        <is>
-          <t>Настройка CI/CD</t>
-        </is>
-      </c>
-      <c r="C7" s="95" t="inlineStr">
-        <is>
-          <t>Новиков А.</t>
-        </is>
-      </c>
-      <c r="D7" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E7" s="96" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G7" s="23">
-        <f>IF(F7="Готово",0,IF(E7="","",E7))</f>
-        <v/>
-      </c>
-      <c r="H7" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C7,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="97" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="72">
-        <f>IF(AND(I7&lt;&gt;"",E7&lt;&gt;""),I7/E7,"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L7" s="33" t="n"/>
-      <c r="M7" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O7" s="128" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P7" s="128" t="n">
-        <v>46237</v>
-      </c>
-      <c r="Q7" s="128" t="n">
-        <v>46239</v>
-      </c>
-      <c r="R7" s="90">
-        <f>IF(AND(Q7&lt;&gt;"",P7&lt;&gt;""),Q7-P7,"")</f>
-        <v/>
-      </c>
-      <c r="S7" s="90">
-        <f>IF(AND(Q7&lt;&gt;"",O7&lt;&gt;""),Q7-O7,"")</f>
-        <v/>
-      </c>
-      <c r="T7" s="90">
-        <f>IF(AND(F7="В работе",P7&lt;&gt;""),Параметры!$B$10-P7,"")</f>
-        <v/>
-      </c>
-      <c r="U7" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="94" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B8" s="95" t="inlineStr">
-        <is>
-          <t>Модель данных заказа</t>
-        </is>
-      </c>
-      <c r="C8" s="95" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="D8" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E8" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="94" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="G8" s="23">
-        <f>IF(F8="Готово",0,IF(E8="","",E8))</f>
-        <v/>
-      </c>
-      <c r="H8" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C8,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="97" t="n"/>
-      <c r="J8" s="72">
-        <f>IF(AND(I8&lt;&gt;"",E8&lt;&gt;""),I8/E8,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O8" s="128" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P8" s="128" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Q8" s="129" t="n"/>
-      <c r="R8" s="90">
-        <f>IF(AND(Q8&lt;&gt;"",P8&lt;&gt;""),Q8-P8,"")</f>
-        <v/>
-      </c>
-      <c r="S8" s="90">
-        <f>IF(AND(Q8&lt;&gt;"",O8&lt;&gt;""),Q8-O8,"")</f>
-        <v/>
-      </c>
-      <c r="T8" s="90">
-        <f>IF(AND(F8="В работе",P8&lt;&gt;""),Параметры!$B$10-P8,"")</f>
-        <v/>
-      </c>
-      <c r="U8" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="94" t="inlineStr">
-        <is>
-          <t>T-03</t>
-        </is>
-      </c>
-      <c r="B9" s="95" t="inlineStr">
-        <is>
-          <t>Интеграция платежей</t>
-        </is>
-      </c>
-      <c r="C9" s="95" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="D9" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E9" s="96" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G9" s="23">
-        <f>IF(F9="Готово",0,IF(E9="","",E9))</f>
-        <v/>
-      </c>
-      <c r="H9" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C9,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="97" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="72">
-        <f>IF(AND(I9&lt;&gt;"",E9&lt;&gt;""),I9/E9,"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O9" s="128" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P9" s="128" t="n">
-        <v>46251</v>
-      </c>
-      <c r="Q9" s="128" t="n">
-        <v>46258</v>
-      </c>
-      <c r="R9" s="90">
-        <f>IF(AND(Q9&lt;&gt;"",P9&lt;&gt;""),Q9-P9,"")</f>
-        <v/>
-      </c>
-      <c r="S9" s="90">
-        <f>IF(AND(Q9&lt;&gt;"",O9&lt;&gt;""),Q9-O9,"")</f>
-        <v/>
-      </c>
-      <c r="T9" s="90">
-        <f>IF(AND(F9="В работе",P9&lt;&gt;""),Параметры!$B$10-P9,"")</f>
-        <v/>
-      </c>
-      <c r="U9" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="94" t="inlineStr">
-        <is>
-          <t>T-04</t>
-        </is>
-      </c>
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Тест-кейсы оформления</t>
-        </is>
-      </c>
-      <c r="C10" s="95" t="inlineStr">
-        <is>
-          <t>Сидоров К.</t>
-        </is>
-      </c>
-      <c r="D10" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E10" s="96" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G10" s="23">
-        <f>IF(F10="Готово",0,IF(E10="","",E10))</f>
-        <v/>
-      </c>
-      <c r="H10" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C10,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="97" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="72">
-        <f>IF(AND(I10&lt;&gt;"",E10&lt;&gt;""),I10/E10,"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O10" s="128" t="n">
-        <v>46246</v>
-      </c>
-      <c r="P10" s="128" t="n">
-        <v>46252</v>
-      </c>
-      <c r="Q10" s="128" t="n">
-        <v>46254</v>
-      </c>
-      <c r="R10" s="90">
-        <f>IF(AND(Q10&lt;&gt;"",P10&lt;&gt;""),Q10-P10,"")</f>
-        <v/>
-      </c>
-      <c r="S10" s="90">
-        <f>IF(AND(Q10&lt;&gt;"",O10&lt;&gt;""),Q10-O10,"")</f>
-        <v/>
-      </c>
-      <c r="T10" s="90">
-        <f>IF(AND(F10="В работе",P10&lt;&gt;""),Параметры!$B$10-P10,"")</f>
-        <v/>
-      </c>
-      <c r="U10" s="201" t="inlineStr">
-        <is>
-          <t>Тех.долг</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="94" t="inlineStr">
-        <is>
-          <t>T-08</t>
-        </is>
-      </c>
-      <c r="B11" s="95" t="inlineStr">
-        <is>
-          <t>Уведомления по e-mail</t>
-        </is>
-      </c>
-      <c r="C11" s="95" t="inlineStr">
-        <is>
-          <t>Смирнов П.</t>
-        </is>
-      </c>
-      <c r="D11" s="94" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E11" s="96" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G11" s="23">
-        <f>IF(F11="Готово",0,IF(E11="","",E11))</f>
-        <v/>
-      </c>
-      <c r="H11" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C11,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="97" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="72">
-        <f>IF(AND(I11&lt;&gt;"",E11&lt;&gt;""),I11/E11,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O11" s="128" t="n">
-        <v>46246</v>
-      </c>
-      <c r="P11" s="128" t="n">
-        <v>46253</v>
-      </c>
-      <c r="Q11" s="128" t="n">
-        <v>46260</v>
-      </c>
-      <c r="R11" s="90">
-        <f>IF(AND(Q11&lt;&gt;"",P11&lt;&gt;""),Q11-P11,"")</f>
-        <v/>
-      </c>
-      <c r="S11" s="90">
-        <f>IF(AND(Q11&lt;&gt;"",O11&lt;&gt;""),Q11-O11,"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="90">
-        <f>IF(AND(F11="В работе",P11&lt;&gt;""),Параметры!$B$10-P11,"")</f>
-        <v/>
-      </c>
-      <c r="U11" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="94" t="inlineStr">
-        <is>
-          <t>T-11</t>
-        </is>
-      </c>
-      <c r="B12" s="95" t="inlineStr">
-        <is>
-          <t>API промокодов</t>
-        </is>
-      </c>
-      <c r="C12" s="95" t="inlineStr">
-        <is>
-          <t>Козлов В.</t>
-        </is>
-      </c>
-      <c r="D12" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E12" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="94" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="G12" s="23">
-        <f>IF(F12="Готово",0,IF(E12="","",E12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C12,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="97" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="72">
-        <f>IF(AND(I12&lt;&gt;"",E12&lt;&gt;""),I12/E12,"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O12" s="128" t="n">
-        <v>46245</v>
-      </c>
-      <c r="P12" s="128" t="n">
-        <v>46251</v>
-      </c>
-      <c r="Q12" s="128" t="n">
-        <v>46259</v>
-      </c>
-      <c r="R12" s="90">
-        <f>IF(AND(Q12&lt;&gt;"",P12&lt;&gt;""),Q12-P12,"")</f>
-        <v/>
-      </c>
-      <c r="S12" s="90">
-        <f>IF(AND(Q12&lt;&gt;"",O12&lt;&gt;""),Q12-O12,"")</f>
-        <v/>
-      </c>
-      <c r="T12" s="90">
-        <f>IF(AND(F12="В работе",P12&lt;&gt;""),Параметры!$B$10-P12,"")</f>
-        <v/>
-      </c>
-      <c r="U12" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="94" t="inlineStr">
-        <is>
-          <t>T-12</t>
-        </is>
-      </c>
-      <c r="B13" s="95" t="inlineStr">
-        <is>
-          <t>Логирование и метрики</t>
-        </is>
-      </c>
-      <c r="C13" s="95" t="inlineStr">
-        <is>
-          <t>Новиков А.</t>
-        </is>
-      </c>
-      <c r="D13" s="94" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E13" s="96" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G13" s="23">
-        <f>IF(F13="Готово",0,IF(E13="","",E13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C13,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="97" t="n"/>
-      <c r="J13" s="72">
-        <f>IF(AND(I13&lt;&gt;"",E13&lt;&gt;""),I13/E13,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="98" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O13" s="129" t="n"/>
-      <c r="P13" s="129" t="n"/>
-      <c r="Q13" s="129" t="n"/>
-      <c r="R13" s="90">
-        <f>IF(AND(Q13&lt;&gt;"",P13&lt;&gt;""),Q13-P13,"")</f>
-        <v/>
-      </c>
-      <c r="S13" s="90">
-        <f>IF(AND(Q13&lt;&gt;"",O13&lt;&gt;""),Q13-O13,"")</f>
-        <v/>
-      </c>
-      <c r="T13" s="90">
-        <f>IF(AND(F13="В работе",P13&lt;&gt;""),Параметры!$B$10-P13,"")</f>
-        <v/>
-      </c>
-      <c r="U13" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="94" t="inlineStr">
-        <is>
-          <t>T-05</t>
-        </is>
-      </c>
-      <c r="B14" s="95" t="inlineStr">
-        <is>
-          <t>Рефакторинг авторизации</t>
-        </is>
-      </c>
-      <c r="C14" s="95" t="inlineStr">
-        <is>
-          <t>Кузнецов Д.</t>
-        </is>
-      </c>
-      <c r="D14" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E14" s="96" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="94" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="G14" s="23">
-        <f>IF(F14="Готово",0,IF(E14="","",E14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C14,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="97" t="n"/>
-      <c r="J14" s="72">
-        <f>IF(AND(I14&lt;&gt;"",E14&lt;&gt;""),I14/E14,"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O14" s="128" t="n">
-        <v>46262</v>
-      </c>
-      <c r="P14" s="128" t="n">
-        <v>46267</v>
-      </c>
-      <c r="Q14" s="129" t="n"/>
-      <c r="R14" s="90">
-        <f>IF(AND(Q14&lt;&gt;"",P14&lt;&gt;""),Q14-P14,"")</f>
-        <v/>
-      </c>
-      <c r="S14" s="90">
-        <f>IF(AND(Q14&lt;&gt;"",O14&lt;&gt;""),Q14-O14,"")</f>
-        <v/>
-      </c>
-      <c r="T14" s="90">
-        <f>IF(AND(F14="В работе",P14&lt;&gt;""),Параметры!$B$10-P14,"")</f>
-        <v/>
-      </c>
-      <c r="U14" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="94" t="inlineStr">
-        <is>
-          <t>T-06</t>
-        </is>
-      </c>
-      <c r="B15" s="95" t="inlineStr">
-        <is>
-          <t>Аналитика воронки</t>
-        </is>
-      </c>
-      <c r="C15" s="95" t="inlineStr">
-        <is>
-          <t>Орлова Е.</t>
-        </is>
-      </c>
-      <c r="D15" s="94" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E15" s="96" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G15" s="23">
-        <f>IF(F15="Готово",0,IF(E15="","",E15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C15,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="97" t="n"/>
-      <c r="J15" s="72">
-        <f>IF(AND(I15&lt;&gt;"",E15&lt;&gt;""),I15/E15,"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="109" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="O15" s="129" t="n"/>
-      <c r="P15" s="129" t="n"/>
-      <c r="Q15" s="129" t="n"/>
-      <c r="R15" s="90">
-        <f>IF(AND(Q15&lt;&gt;"",P15&lt;&gt;""),Q15-P15,"")</f>
-        <v/>
-      </c>
-      <c r="S15" s="90">
-        <f>IF(AND(Q15&lt;&gt;"",O15&lt;&gt;""),Q15-O15,"")</f>
-        <v/>
-      </c>
-      <c r="T15" s="90">
-        <f>IF(AND(F15="В работе",P15&lt;&gt;""),Параметры!$B$10-P15,"")</f>
-        <v/>
-      </c>
-      <c r="U15" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="94" t="inlineStr">
-        <is>
-          <t>T-07</t>
-        </is>
-      </c>
-      <c r="B16" s="95" t="inlineStr">
-        <is>
-          <t>Регресс-тестирование релиза</t>
-        </is>
-      </c>
-      <c r="C16" s="95" t="inlineStr">
-        <is>
-          <t>Сидоров К.</t>
-        </is>
-      </c>
-      <c r="D16" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E16" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G16" s="23">
-        <f>IF(F16="Готово",0,IF(E16="","",E16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C16,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="97" t="n"/>
-      <c r="J16" s="72">
-        <f>IF(AND(I16&lt;&gt;"",E16&lt;&gt;""),I16/E16,"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L16" s="33" t="n"/>
-      <c r="M16" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O16" s="129" t="n"/>
-      <c r="P16" s="129" t="n"/>
-      <c r="Q16" s="129" t="n"/>
-      <c r="R16" s="90">
-        <f>IF(AND(Q16&lt;&gt;"",P16&lt;&gt;""),Q16-P16,"")</f>
-        <v/>
-      </c>
-      <c r="S16" s="90">
-        <f>IF(AND(Q16&lt;&gt;"",O16&lt;&gt;""),Q16-O16,"")</f>
-        <v/>
-      </c>
-      <c r="T16" s="90">
-        <f>IF(AND(F16="В работе",P16&lt;&gt;""),Параметры!$B$10-P16,"")</f>
-        <v/>
-      </c>
-      <c r="U16" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="94" t="inlineStr">
-        <is>
-          <t>T-13</t>
-        </is>
-      </c>
-      <c r="B17" s="95" t="inlineStr">
-        <is>
-          <t>Экран оплаты</t>
-        </is>
-      </c>
-      <c r="C17" s="95" t="inlineStr">
-        <is>
-          <t>Волкова Н.</t>
-        </is>
-      </c>
-      <c r="D17" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E17" s="96" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="94" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="G17" s="23">
-        <f>IF(F17="Готово",0,IF(E17="","",E17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C17,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="97" t="n"/>
-      <c r="J17" s="72">
-        <f>IF(AND(I17&lt;&gt;"",E17&lt;&gt;""),I17/E17,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L17" s="33" t="n"/>
-      <c r="M17" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O17" s="128" t="n">
-        <v>46262</v>
-      </c>
-      <c r="P17" s="128" t="n">
-        <v>46266</v>
-      </c>
-      <c r="Q17" s="129" t="n"/>
-      <c r="R17" s="90">
-        <f>IF(AND(Q17&lt;&gt;"",P17&lt;&gt;""),Q17-P17,"")</f>
-        <v/>
-      </c>
-      <c r="S17" s="90">
-        <f>IF(AND(Q17&lt;&gt;"",O17&lt;&gt;""),Q17-O17,"")</f>
-        <v/>
-      </c>
-      <c r="T17" s="90">
-        <f>IF(AND(F17="В работе",P17&lt;&gt;""),Параметры!$B$10-P17,"")</f>
-        <v/>
-      </c>
-      <c r="U17" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="94" t="inlineStr">
-        <is>
-          <t>T-14</t>
-        </is>
-      </c>
-      <c r="B18" s="95" t="inlineStr">
-        <is>
-          <t>Вебхуки платежей</t>
-        </is>
-      </c>
-      <c r="C18" s="95" t="inlineStr">
-        <is>
-          <t>Иванов А.</t>
-        </is>
-      </c>
-      <c r="D18" s="94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E18" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G18" s="23">
-        <f>IF(F18="Готово",0,IF(E18="","",E18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C18,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="97" t="n"/>
-      <c r="J18" s="72">
-        <f>IF(AND(I18&lt;&gt;"",E18&lt;&gt;""),I18/E18,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="99" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="L18" s="100" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="109" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="O18" s="129" t="n"/>
-      <c r="P18" s="129" t="n"/>
-      <c r="Q18" s="129" t="n"/>
-      <c r="R18" s="90">
-        <f>IF(AND(Q18&lt;&gt;"",P18&lt;&gt;""),Q18-P18,"")</f>
-        <v/>
-      </c>
-      <c r="S18" s="90">
-        <f>IF(AND(Q18&lt;&gt;"",O18&lt;&gt;""),Q18-O18,"")</f>
-        <v/>
-      </c>
-      <c r="T18" s="90">
-        <f>IF(AND(F18="В работе",P18&lt;&gt;""),Параметры!$B$10-P18,"")</f>
-        <v/>
-      </c>
-      <c r="U18" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="94" t="inlineStr">
-        <is>
-          <t>T-15</t>
-        </is>
-      </c>
-      <c r="B19" s="95" t="inlineStr">
-        <is>
-          <t>История заказов</t>
-        </is>
-      </c>
-      <c r="C19" s="95" t="inlineStr">
-        <is>
-          <t>Соколов Р.</t>
-        </is>
-      </c>
-      <c r="D19" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E19" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G19" s="23">
-        <f>IF(F19="Готово",0,IF(E19="","",E19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C19,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="97" t="n"/>
-      <c r="J19" s="72">
-        <f>IF(AND(I19&lt;&gt;"",E19&lt;&gt;""),I19/E19,"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L19" s="33" t="n"/>
-      <c r="M19" s="98" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O19" s="129" t="n"/>
-      <c r="P19" s="129" t="n"/>
-      <c r="Q19" s="129" t="n"/>
-      <c r="R19" s="90">
-        <f>IF(AND(Q19&lt;&gt;"",P19&lt;&gt;""),Q19-P19,"")</f>
-        <v/>
-      </c>
-      <c r="S19" s="90">
-        <f>IF(AND(Q19&lt;&gt;"",O19&lt;&gt;""),Q19-O19,"")</f>
-        <v/>
-      </c>
-      <c r="T19" s="90">
-        <f>IF(AND(F19="В работе",P19&lt;&gt;""),Параметры!$B$10-P19,"")</f>
-        <v/>
-      </c>
-      <c r="U19" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="94" t="inlineStr">
-        <is>
-          <t>T-16</t>
-        </is>
-      </c>
-      <c r="B20" s="95" t="inlineStr">
-        <is>
-          <t>Личный кабинет</t>
-        </is>
-      </c>
-      <c r="C20" s="95" t="inlineStr">
-        <is>
-          <t>Волкова Н.</t>
-        </is>
-      </c>
-      <c r="D20" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E20" s="96" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G20" s="23">
-        <f>IF(F20="Готово",0,IF(E20="","",E20))</f>
-        <v/>
-      </c>
-      <c r="H20" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C20,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="97" t="n"/>
-      <c r="J20" s="72">
-        <f>IF(AND(I20&lt;&gt;"",E20&lt;&gt;""),I20/E20,"")</f>
-        <v/>
-      </c>
-      <c r="K20" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L20" s="33" t="n"/>
-      <c r="M20" s="98" t="n">
-        <v>4</v>
-      </c>
-      <c r="N20" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O20" s="129" t="n"/>
-      <c r="P20" s="129" t="n"/>
-      <c r="Q20" s="129" t="n"/>
-      <c r="R20" s="90">
-        <f>IF(AND(Q20&lt;&gt;"",P20&lt;&gt;""),Q20-P20,"")</f>
-        <v/>
-      </c>
-      <c r="S20" s="90">
-        <f>IF(AND(Q20&lt;&gt;"",O20&lt;&gt;""),Q20-O20,"")</f>
-        <v/>
-      </c>
-      <c r="T20" s="90">
-        <f>IF(AND(F20="В работе",P20&lt;&gt;""),Параметры!$B$10-P20,"")</f>
-        <v/>
-      </c>
-      <c r="U20" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="94" t="inlineStr">
-        <is>
-          <t>T-17</t>
-        </is>
-      </c>
-      <c r="B21" s="95" t="inlineStr">
-        <is>
-          <t>Фильтры каталога</t>
-        </is>
-      </c>
-      <c r="C21" s="95" t="inlineStr">
-        <is>
-          <t>Морозов И.</t>
-        </is>
-      </c>
-      <c r="D21" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E21" s="96" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G21" s="23">
-        <f>IF(F21="Готово",0,IF(E21="","",E21))</f>
-        <v/>
-      </c>
-      <c r="H21" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C21,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="97" t="n"/>
-      <c r="J21" s="72">
-        <f>IF(AND(I21&lt;&gt;"",E21&lt;&gt;""),I21/E21,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L21" s="33" t="n"/>
-      <c r="M21" s="98" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O21" s="129" t="n"/>
-      <c r="P21" s="129" t="n"/>
-      <c r="Q21" s="129" t="n"/>
-      <c r="R21" s="90">
-        <f>IF(AND(Q21&lt;&gt;"",P21&lt;&gt;""),Q21-P21,"")</f>
-        <v/>
-      </c>
-      <c r="S21" s="90">
-        <f>IF(AND(Q21&lt;&gt;"",O21&lt;&gt;""),Q21-O21,"")</f>
-        <v/>
-      </c>
-      <c r="T21" s="90">
-        <f>IF(AND(F21="В работе",P21&lt;&gt;""),Параметры!$B$10-P21,"")</f>
-        <v/>
-      </c>
-      <c r="U21" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="94" t="inlineStr">
-        <is>
-          <t>T-18</t>
-        </is>
-      </c>
-      <c r="B22" s="95" t="inlineStr">
-        <is>
-          <t>Отзывы и рейтинги</t>
-        </is>
-      </c>
-      <c r="C22" s="95" t="inlineStr">
-        <is>
-          <t>Лебедева Т.</t>
-        </is>
-      </c>
-      <c r="D22" s="94" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E22" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G22" s="23">
-        <f>IF(F22="Готово",0,IF(E22="","",E22))</f>
-        <v/>
-      </c>
-      <c r="H22" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C22,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="97" t="n"/>
-      <c r="J22" s="72">
-        <f>IF(AND(I22&lt;&gt;"",E22&lt;&gt;""),I22/E22,"")</f>
-        <v/>
-      </c>
-      <c r="K22" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L22" s="33" t="n"/>
-      <c r="M22" s="98" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O22" s="129" t="n"/>
-      <c r="P22" s="129" t="n"/>
-      <c r="Q22" s="129" t="n"/>
-      <c r="R22" s="90">
-        <f>IF(AND(Q22&lt;&gt;"",P22&lt;&gt;""),Q22-P22,"")</f>
-        <v/>
-      </c>
-      <c r="S22" s="90">
-        <f>IF(AND(Q22&lt;&gt;"",O22&lt;&gt;""),Q22-O22,"")</f>
-        <v/>
-      </c>
-      <c r="T22" s="90">
-        <f>IF(AND(F22="В работе",P22&lt;&gt;""),Параметры!$B$10-P22,"")</f>
-        <v/>
-      </c>
-      <c r="U22" s="201" t="inlineStr">
-        <is>
-          <t>Тех.долг</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="94" t="inlineStr">
-        <is>
-          <t>T-19</t>
-        </is>
-      </c>
-      <c r="B23" s="95" t="inlineStr">
-        <is>
-          <t>Рекомендации</t>
-        </is>
-      </c>
-      <c r="C23" s="95" t="inlineStr">
-        <is>
-          <t>Фёдорова О.</t>
-        </is>
-      </c>
-      <c r="D23" s="94" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E23" s="96" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G23" s="23">
-        <f>IF(F23="Готово",0,IF(E23="","",E23))</f>
-        <v/>
-      </c>
-      <c r="H23" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C23,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="97" t="n"/>
-      <c r="J23" s="72">
-        <f>IF(AND(I23&lt;&gt;"",E23&lt;&gt;""),I23/E23,"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L23" s="33" t="n"/>
-      <c r="M23" s="98" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O23" s="129" t="n"/>
-      <c r="P23" s="129" t="n"/>
-      <c r="Q23" s="129" t="n"/>
-      <c r="R23" s="90">
-        <f>IF(AND(Q23&lt;&gt;"",P23&lt;&gt;""),Q23-P23,"")</f>
-        <v/>
-      </c>
-      <c r="S23" s="90">
-        <f>IF(AND(Q23&lt;&gt;"",O23&lt;&gt;""),Q23-O23,"")</f>
-        <v/>
-      </c>
-      <c r="T23" s="90">
-        <f>IF(AND(F23="В работе",P23&lt;&gt;""),Параметры!$B$10-P23,"")</f>
-        <v/>
-      </c>
-      <c r="U23" s="201" t="inlineStr">
-        <is>
-          <t>История</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="94" t="inlineStr">
-        <is>
-          <t>T-20</t>
-        </is>
-      </c>
-      <c r="B24" s="95" t="inlineStr">
-        <is>
-          <t>A/B тесты чекаута</t>
-        </is>
-      </c>
-      <c r="C24" s="95" t="inlineStr">
-        <is>
-          <t>Морозов И.</t>
-        </is>
-      </c>
-      <c r="D24" s="94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E24" s="96" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="94" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G24" s="23">
-        <f>IF(F24="Готово",0,IF(E24="","",E24))</f>
-        <v/>
-      </c>
-      <c r="H24" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C24,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="97" t="n"/>
-      <c r="J24" s="72">
-        <f>IF(AND(I24&lt;&gt;"",E24&lt;&gt;""),I24/E24,"")</f>
-        <v/>
-      </c>
-      <c r="K24" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L24" s="33" t="n"/>
-      <c r="M24" s="98" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="109" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O24" s="129" t="n"/>
-      <c r="P24" s="129" t="n"/>
-      <c r="Q24" s="129" t="n"/>
-      <c r="R24" s="90">
-        <f>IF(AND(Q24&lt;&gt;"",P24&lt;&gt;""),Q24-P24,"")</f>
-        <v/>
-      </c>
-      <c r="S24" s="90">
-        <f>IF(AND(Q24&lt;&gt;"",O24&lt;&gt;""),Q24-O24,"")</f>
-        <v/>
-      </c>
-      <c r="T24" s="90">
-        <f>IF(AND(F24="В работе",P24&lt;&gt;""),Параметры!$B$10-P24,"")</f>
-        <v/>
-      </c>
-      <c r="U24" s="201" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="23">
-        <f>IF(F25="Готово",0,IF(E25="","",E25))</f>
-        <v/>
-      </c>
-      <c r="H25" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C25,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="71" t="n"/>
-      <c r="J25" s="72">
-        <f>IF(AND(I25&lt;&gt;"",E25&lt;&gt;""),I25/E25,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L25" s="33" t="n"/>
-      <c r="M25" s="101" t="n"/>
-      <c r="N25" s="109" t="n"/>
-      <c r="O25" s="129" t="n"/>
-      <c r="P25" s="129" t="n"/>
-      <c r="Q25" s="129" t="n"/>
-      <c r="R25" s="90">
-        <f>IF(AND(Q25&lt;&gt;"",P25&lt;&gt;""),Q25-P25,"")</f>
-        <v/>
-      </c>
-      <c r="S25" s="90">
-        <f>IF(AND(Q25&lt;&gt;"",O25&lt;&gt;""),Q25-O25,"")</f>
-        <v/>
-      </c>
-      <c r="T25" s="90">
-        <f>IF(AND(F25="В работе",P25&lt;&gt;""),Параметры!$B$10-P25,"")</f>
-        <v/>
-      </c>
-      <c r="U25" s="211" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="23">
-        <f>IF(F26="Готово",0,IF(E26="","",E26))</f>
-        <v/>
-      </c>
-      <c r="H26" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C26,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="71" t="n"/>
-      <c r="J26" s="72">
-        <f>IF(AND(I26&lt;&gt;"",E26&lt;&gt;""),I26/E26,"")</f>
-        <v/>
-      </c>
-      <c r="K26" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L26" s="33" t="n"/>
-      <c r="M26" s="101" t="n"/>
-      <c r="N26" s="109" t="n"/>
-      <c r="O26" s="129" t="n"/>
-      <c r="P26" s="129" t="n"/>
-      <c r="Q26" s="129" t="n"/>
-      <c r="R26" s="90">
-        <f>IF(AND(Q26&lt;&gt;"",P26&lt;&gt;""),Q26-P26,"")</f>
-        <v/>
-      </c>
-      <c r="S26" s="90">
-        <f>IF(AND(Q26&lt;&gt;"",O26&lt;&gt;""),Q26-O26,"")</f>
-        <v/>
-      </c>
-      <c r="T26" s="90">
-        <f>IF(AND(F26="В работе",P26&lt;&gt;""),Параметры!$B$10-P26,"")</f>
-        <v/>
-      </c>
-      <c r="U26" s="211" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="23">
-        <f>IF(F27="Готово",0,IF(E27="","",E27))</f>
-        <v/>
-      </c>
-      <c r="H27" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C27,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="71" t="n"/>
-      <c r="J27" s="72">
-        <f>IF(AND(I27&lt;&gt;"",E27&lt;&gt;""),I27/E27,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L27" s="33" t="n"/>
-      <c r="M27" s="101" t="n"/>
-      <c r="N27" s="109" t="n"/>
-      <c r="O27" s="129" t="n"/>
-      <c r="P27" s="129" t="n"/>
-      <c r="Q27" s="129" t="n"/>
-      <c r="R27" s="90">
-        <f>IF(AND(Q27&lt;&gt;"",P27&lt;&gt;""),Q27-P27,"")</f>
-        <v/>
-      </c>
-      <c r="S27" s="90">
-        <f>IF(AND(Q27&lt;&gt;"",O27&lt;&gt;""),Q27-O27,"")</f>
-        <v/>
-      </c>
-      <c r="T27" s="90">
-        <f>IF(AND(F27="В работе",P27&lt;&gt;""),Параметры!$B$10-P27,"")</f>
-        <v/>
-      </c>
-      <c r="U27" s="211" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="23">
-        <f>IF(F28="Готово",0,IF(E28="","",E28))</f>
-        <v/>
-      </c>
-      <c r="H28" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C28,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="71" t="n"/>
-      <c r="J28" s="72">
-        <f>IF(AND(I28&lt;&gt;"",E28&lt;&gt;""),I28/E28,"")</f>
-        <v/>
-      </c>
-      <c r="K28" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L28" s="33" t="n"/>
-      <c r="M28" s="101" t="n"/>
-      <c r="N28" s="109" t="n"/>
-      <c r="O28" s="129" t="n"/>
-      <c r="P28" s="129" t="n"/>
-      <c r="Q28" s="129" t="n"/>
-      <c r="R28" s="90">
-        <f>IF(AND(Q28&lt;&gt;"",P28&lt;&gt;""),Q28-P28,"")</f>
-        <v/>
-      </c>
-      <c r="S28" s="90">
-        <f>IF(AND(Q28&lt;&gt;"",O28&lt;&gt;""),Q28-O28,"")</f>
-        <v/>
-      </c>
-      <c r="T28" s="90">
-        <f>IF(AND(F28="В работе",P28&lt;&gt;""),Параметры!$B$10-P28,"")</f>
-        <v/>
-      </c>
-      <c r="U28" s="211" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="23">
-        <f>IF(F29="Готово",0,IF(E29="","",E29))</f>
-        <v/>
-      </c>
-      <c r="H29" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C29,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="71" t="n"/>
-      <c r="J29" s="72">
-        <f>IF(AND(I29&lt;&gt;"",E29&lt;&gt;""),I29/E29,"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L29" s="33" t="n"/>
-      <c r="M29" s="101" t="n"/>
-      <c r="N29" s="109" t="n"/>
-      <c r="O29" s="129" t="n"/>
-      <c r="P29" s="129" t="n"/>
-      <c r="Q29" s="129" t="n"/>
-      <c r="R29" s="90">
-        <f>IF(AND(Q29&lt;&gt;"",P29&lt;&gt;""),Q29-P29,"")</f>
-        <v/>
-      </c>
-      <c r="S29" s="90">
-        <f>IF(AND(Q29&lt;&gt;"",O29&lt;&gt;""),Q29-O29,"")</f>
-        <v/>
-      </c>
-      <c r="T29" s="90">
-        <f>IF(AND(F29="В работе",P29&lt;&gt;""),Параметры!$B$10-P29,"")</f>
-        <v/>
-      </c>
-      <c r="U29" s="211" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="23">
-        <f>IF(F30="Готово",0,IF(E30="","",E30))</f>
-        <v/>
-      </c>
-      <c r="H30" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C30,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="71" t="n"/>
-      <c r="J30" s="72">
-        <f>IF(AND(I30&lt;&gt;"",E30&lt;&gt;""),I30/E30,"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L30" s="33" t="n"/>
-      <c r="M30" s="101" t="n"/>
-      <c r="N30" s="109" t="n"/>
-      <c r="O30" s="129" t="n"/>
-      <c r="P30" s="129" t="n"/>
-      <c r="Q30" s="129" t="n"/>
-      <c r="R30" s="90">
-        <f>IF(AND(Q30&lt;&gt;"",P30&lt;&gt;""),Q30-P30,"")</f>
-        <v/>
-      </c>
-      <c r="S30" s="90">
-        <f>IF(AND(Q30&lt;&gt;"",O30&lt;&gt;""),Q30-O30,"")</f>
-        <v/>
-      </c>
-      <c r="T30" s="90">
-        <f>IF(AND(F30="В работе",P30&lt;&gt;""),Параметры!$B$10-P30,"")</f>
-        <v/>
-      </c>
-      <c r="U30" s="211" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="23">
-        <f>IF(F31="Готово",0,IF(E31="","",E31))</f>
-        <v/>
-      </c>
-      <c r="H31" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C31,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="71" t="n"/>
-      <c r="J31" s="72">
-        <f>IF(AND(I31&lt;&gt;"",E31&lt;&gt;""),I31/E31,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L31" s="33" t="n"/>
-      <c r="M31" s="101" t="n"/>
-      <c r="N31" s="109" t="n"/>
-      <c r="O31" s="129" t="n"/>
-      <c r="P31" s="129" t="n"/>
-      <c r="Q31" s="129" t="n"/>
-      <c r="R31" s="90">
-        <f>IF(AND(Q31&lt;&gt;"",P31&lt;&gt;""),Q31-P31,"")</f>
-        <v/>
-      </c>
-      <c r="S31" s="90">
-        <f>IF(AND(Q31&lt;&gt;"",O31&lt;&gt;""),Q31-O31,"")</f>
-        <v/>
-      </c>
-      <c r="T31" s="90">
-        <f>IF(AND(F31="В работе",P31&lt;&gt;""),Параметры!$B$10-P31,"")</f>
-        <v/>
-      </c>
-      <c r="U31" s="211" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="23">
-        <f>IF(F32="Готово",0,IF(E32="","",E32))</f>
-        <v/>
-      </c>
-      <c r="H32" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C32,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="71" t="n"/>
-      <c r="J32" s="72">
-        <f>IF(AND(I32&lt;&gt;"",E32&lt;&gt;""),I32/E32,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L32" s="33" t="n"/>
-      <c r="M32" s="101" t="n"/>
-      <c r="N32" s="109" t="n"/>
-      <c r="O32" s="129" t="n"/>
-      <c r="P32" s="129" t="n"/>
-      <c r="Q32" s="129" t="n"/>
-      <c r="R32" s="90">
-        <f>IF(AND(Q32&lt;&gt;"",P32&lt;&gt;""),Q32-P32,"")</f>
-        <v/>
-      </c>
-      <c r="S32" s="90">
-        <f>IF(AND(Q32&lt;&gt;"",O32&lt;&gt;""),Q32-O32,"")</f>
-        <v/>
-      </c>
-      <c r="T32" s="90">
-        <f>IF(AND(F32="В работе",P32&lt;&gt;""),Параметры!$B$10-P32,"")</f>
-        <v/>
-      </c>
-      <c r="U32" s="211" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="23">
-        <f>IF(F33="Готово",0,IF(E33="","",E33))</f>
-        <v/>
-      </c>
-      <c r="H33" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C33,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="71" t="n"/>
-      <c r="J33" s="72">
-        <f>IF(AND(I33&lt;&gt;"",E33&lt;&gt;""),I33/E33,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="101" t="n"/>
-      <c r="N33" s="109" t="n"/>
-      <c r="O33" s="129" t="n"/>
-      <c r="P33" s="129" t="n"/>
-      <c r="Q33" s="129" t="n"/>
-      <c r="R33" s="90">
-        <f>IF(AND(Q33&lt;&gt;"",P33&lt;&gt;""),Q33-P33,"")</f>
-        <v/>
-      </c>
-      <c r="S33" s="90">
-        <f>IF(AND(Q33&lt;&gt;"",O33&lt;&gt;""),Q33-O33,"")</f>
-        <v/>
-      </c>
-      <c r="T33" s="90">
-        <f>IF(AND(F33="В работе",P33&lt;&gt;""),Параметры!$B$10-P33,"")</f>
-        <v/>
-      </c>
-      <c r="U33" s="211" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="23">
-        <f>IF(F34="Готово",0,IF(E34="","",E34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C34,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="71" t="n"/>
-      <c r="J34" s="72">
-        <f>IF(AND(I34&lt;&gt;"",E34&lt;&gt;""),I34/E34,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="101" t="n"/>
-      <c r="N34" s="109" t="n"/>
-      <c r="O34" s="129" t="n"/>
-      <c r="P34" s="129" t="n"/>
-      <c r="Q34" s="129" t="n"/>
-      <c r="R34" s="90">
-        <f>IF(AND(Q34&lt;&gt;"",P34&lt;&gt;""),Q34-P34,"")</f>
-        <v/>
-      </c>
-      <c r="S34" s="90">
-        <f>IF(AND(Q34&lt;&gt;"",O34&lt;&gt;""),Q34-O34,"")</f>
-        <v/>
-      </c>
-      <c r="T34" s="90">
-        <f>IF(AND(F34="В работе",P34&lt;&gt;""),Параметры!$B$10-P34,"")</f>
-        <v/>
-      </c>
-      <c r="U34" s="211" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="23">
-        <f>IF(F35="Готово",0,IF(E35="","",E35))</f>
-        <v/>
-      </c>
-      <c r="H35" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C35,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="71" t="n"/>
-      <c r="J35" s="72">
-        <f>IF(AND(I35&lt;&gt;"",E35&lt;&gt;""),I35/E35,"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L35" s="33" t="n"/>
-      <c r="M35" s="101" t="n"/>
-      <c r="N35" s="109" t="n"/>
-      <c r="O35" s="129" t="n"/>
-      <c r="P35" s="129" t="n"/>
-      <c r="Q35" s="129" t="n"/>
-      <c r="R35" s="90">
-        <f>IF(AND(Q35&lt;&gt;"",P35&lt;&gt;""),Q35-P35,"")</f>
-        <v/>
-      </c>
-      <c r="S35" s="90">
-        <f>IF(AND(Q35&lt;&gt;"",O35&lt;&gt;""),Q35-O35,"")</f>
-        <v/>
-      </c>
-      <c r="T35" s="90">
-        <f>IF(AND(F35="В работе",P35&lt;&gt;""),Параметры!$B$10-P35,"")</f>
-        <v/>
-      </c>
-      <c r="U35" s="211" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="23">
-        <f>IF(F36="Готово",0,IF(E36="","",E36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C36,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="71" t="n"/>
-      <c r="J36" s="72">
-        <f>IF(AND(I36&lt;&gt;"",E36&lt;&gt;""),I36/E36,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L36" s="33" t="n"/>
-      <c r="M36" s="101" t="n"/>
-      <c r="N36" s="109" t="n"/>
-      <c r="O36" s="129" t="n"/>
-      <c r="P36" s="129" t="n"/>
-      <c r="Q36" s="129" t="n"/>
-      <c r="R36" s="90">
-        <f>IF(AND(Q36&lt;&gt;"",P36&lt;&gt;""),Q36-P36,"")</f>
-        <v/>
-      </c>
-      <c r="S36" s="90">
-        <f>IF(AND(Q36&lt;&gt;"",O36&lt;&gt;""),Q36-O36,"")</f>
-        <v/>
-      </c>
-      <c r="T36" s="90">
-        <f>IF(AND(F36="В работе",P36&lt;&gt;""),Параметры!$B$10-P36,"")</f>
-        <v/>
-      </c>
-      <c r="U36" s="211" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="23">
-        <f>IF(F37="Готово",0,IF(E37="","",E37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C37,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="71" t="n"/>
-      <c r="J37" s="72">
-        <f>IF(AND(I37&lt;&gt;"",E37&lt;&gt;""),I37/E37,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="101" t="n"/>
-      <c r="N37" s="109" t="n"/>
-      <c r="O37" s="129" t="n"/>
-      <c r="P37" s="129" t="n"/>
-      <c r="Q37" s="129" t="n"/>
-      <c r="R37" s="90">
-        <f>IF(AND(Q37&lt;&gt;"",P37&lt;&gt;""),Q37-P37,"")</f>
-        <v/>
-      </c>
-      <c r="S37" s="90">
-        <f>IF(AND(Q37&lt;&gt;"",O37&lt;&gt;""),Q37-O37,"")</f>
-        <v/>
-      </c>
-      <c r="T37" s="90">
-        <f>IF(AND(F37="В работе",P37&lt;&gt;""),Параметры!$B$10-P37,"")</f>
-        <v/>
-      </c>
-      <c r="U37" s="211" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="23">
-        <f>IF(F38="Готово",0,IF(E38="","",E38))</f>
-        <v/>
-      </c>
-      <c r="H38" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C38,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="71" t="n"/>
-      <c r="J38" s="72">
-        <f>IF(AND(I38&lt;&gt;"",E38&lt;&gt;""),I38/E38,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="101" t="n"/>
-      <c r="N38" s="109" t="n"/>
-      <c r="O38" s="129" t="n"/>
-      <c r="P38" s="129" t="n"/>
-      <c r="Q38" s="129" t="n"/>
-      <c r="R38" s="90">
-        <f>IF(AND(Q38&lt;&gt;"",P38&lt;&gt;""),Q38-P38,"")</f>
-        <v/>
-      </c>
-      <c r="S38" s="90">
-        <f>IF(AND(Q38&lt;&gt;"",O38&lt;&gt;""),Q38-O38,"")</f>
-        <v/>
-      </c>
-      <c r="T38" s="90">
-        <f>IF(AND(F38="В работе",P38&lt;&gt;""),Параметры!$B$10-P38,"")</f>
-        <v/>
-      </c>
-      <c r="U38" s="211" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="23">
-        <f>IF(F39="Готово",0,IF(E39="","",E39))</f>
-        <v/>
-      </c>
-      <c r="H39" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C39,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="71" t="n"/>
-      <c r="J39" s="72">
-        <f>IF(AND(I39&lt;&gt;"",E39&lt;&gt;""),I39/E39,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="101" t="n"/>
-      <c r="N39" s="109" t="n"/>
-      <c r="O39" s="129" t="n"/>
-      <c r="P39" s="129" t="n"/>
-      <c r="Q39" s="129" t="n"/>
-      <c r="R39" s="90">
-        <f>IF(AND(Q39&lt;&gt;"",P39&lt;&gt;""),Q39-P39,"")</f>
-        <v/>
-      </c>
-      <c r="S39" s="90">
-        <f>IF(AND(Q39&lt;&gt;"",O39&lt;&gt;""),Q39-O39,"")</f>
-        <v/>
-      </c>
-      <c r="T39" s="90">
-        <f>IF(AND(F39="В работе",P39&lt;&gt;""),Параметры!$B$10-P39,"")</f>
-        <v/>
-      </c>
-      <c r="U39" s="211" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="23">
-        <f>IF(F40="Готово",0,IF(E40="","",E40))</f>
-        <v/>
-      </c>
-      <c r="H40" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C40,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="71" t="n"/>
-      <c r="J40" s="72">
-        <f>IF(AND(I40&lt;&gt;"",E40&lt;&gt;""),I40/E40,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L40" s="33" t="n"/>
-      <c r="M40" s="101" t="n"/>
-      <c r="N40" s="109" t="n"/>
-      <c r="O40" s="129" t="n"/>
-      <c r="P40" s="129" t="n"/>
-      <c r="Q40" s="129" t="n"/>
-      <c r="R40" s="90">
-        <f>IF(AND(Q40&lt;&gt;"",P40&lt;&gt;""),Q40-P40,"")</f>
-        <v/>
-      </c>
-      <c r="S40" s="90">
-        <f>IF(AND(Q40&lt;&gt;"",O40&lt;&gt;""),Q40-O40,"")</f>
-        <v/>
-      </c>
-      <c r="T40" s="90">
-        <f>IF(AND(F40="В работе",P40&lt;&gt;""),Параметры!$B$10-P40,"")</f>
-        <v/>
-      </c>
-      <c r="U40" s="211" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="23">
-        <f>IF(F41="Готово",0,IF(E41="","",E41))</f>
-        <v/>
-      </c>
-      <c r="H41" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C41,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="71" t="n"/>
-      <c r="J41" s="72">
-        <f>IF(AND(I41&lt;&gt;"",E41&lt;&gt;""),I41/E41,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L41" s="33" t="n"/>
-      <c r="M41" s="101" t="n"/>
-      <c r="N41" s="109" t="n"/>
-      <c r="O41" s="129" t="n"/>
-      <c r="P41" s="129" t="n"/>
-      <c r="Q41" s="129" t="n"/>
-      <c r="R41" s="90">
-        <f>IF(AND(Q41&lt;&gt;"",P41&lt;&gt;""),Q41-P41,"")</f>
-        <v/>
-      </c>
-      <c r="S41" s="90">
-        <f>IF(AND(Q41&lt;&gt;"",O41&lt;&gt;""),Q41-O41,"")</f>
-        <v/>
-      </c>
-      <c r="T41" s="90">
-        <f>IF(AND(F41="В работе",P41&lt;&gt;""),Параметры!$B$10-P41,"")</f>
-        <v/>
-      </c>
-      <c r="U41" s="211" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n"/>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="24" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="23">
-        <f>IF(F42="Готово",0,IF(E42="","",E42))</f>
-        <v/>
-      </c>
-      <c r="H42" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C42,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="71" t="n"/>
-      <c r="J42" s="72">
-        <f>IF(AND(I42&lt;&gt;"",E42&lt;&gt;""),I42/E42,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L42" s="33" t="n"/>
-      <c r="M42" s="101" t="n"/>
-      <c r="N42" s="109" t="n"/>
-      <c r="O42" s="129" t="n"/>
-      <c r="P42" s="129" t="n"/>
-      <c r="Q42" s="129" t="n"/>
-      <c r="R42" s="90">
-        <f>IF(AND(Q42&lt;&gt;"",P42&lt;&gt;""),Q42-P42,"")</f>
-        <v/>
-      </c>
-      <c r="S42" s="90">
-        <f>IF(AND(Q42&lt;&gt;"",O42&lt;&gt;""),Q42-O42,"")</f>
-        <v/>
-      </c>
-      <c r="T42" s="90">
-        <f>IF(AND(F42="В работе",P42&lt;&gt;""),Параметры!$B$10-P42,"")</f>
-        <v/>
-      </c>
-      <c r="U42" s="211" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n"/>
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="23">
-        <f>IF(F43="Готово",0,IF(E43="","",E43))</f>
-        <v/>
-      </c>
-      <c r="H43" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C43,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="71" t="n"/>
-      <c r="J43" s="72">
-        <f>IF(AND(I43&lt;&gt;"",E43&lt;&gt;""),I43/E43,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L43" s="33" t="n"/>
-      <c r="M43" s="101" t="n"/>
-      <c r="N43" s="109" t="n"/>
-      <c r="O43" s="129" t="n"/>
-      <c r="P43" s="129" t="n"/>
-      <c r="Q43" s="129" t="n"/>
-      <c r="R43" s="90">
-        <f>IF(AND(Q43&lt;&gt;"",P43&lt;&gt;""),Q43-P43,"")</f>
-        <v/>
-      </c>
-      <c r="S43" s="90">
-        <f>IF(AND(Q43&lt;&gt;"",O43&lt;&gt;""),Q43-O43,"")</f>
-        <v/>
-      </c>
-      <c r="T43" s="90">
-        <f>IF(AND(F43="В работе",P43&lt;&gt;""),Параметры!$B$10-P43,"")</f>
-        <v/>
-      </c>
-      <c r="U43" s="211" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="24" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="23">
-        <f>IF(F44="Готово",0,IF(E44="","",E44))</f>
-        <v/>
-      </c>
-      <c r="H44" s="70">
-        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C44,Капасити!$B$5:$B$147,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="71" t="n"/>
-      <c r="J44" s="72">
-        <f>IF(AND(I44&lt;&gt;"",E44&lt;&gt;""),I44/E44,"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="50" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="L44" s="33" t="n"/>
-      <c r="M44" s="101" t="n"/>
-      <c r="N44" s="109" t="n"/>
-      <c r="O44" s="129" t="n"/>
-      <c r="P44" s="129" t="n"/>
-      <c r="Q44" s="129" t="n"/>
-      <c r="R44" s="90">
-        <f>IF(AND(Q44&lt;&gt;"",P44&lt;&gt;""),Q44-P44,"")</f>
-        <v/>
-      </c>
-      <c r="S44" s="90">
-        <f>IF(AND(Q44&lt;&gt;"",O44&lt;&gt;""),Q44-O44,"")</f>
-        <v/>
-      </c>
-      <c r="T44" s="90">
-        <f>IF(AND(F44="В работе",P44&lt;&gt;""),Параметры!$B$10-P44,"")</f>
-        <v/>
-      </c>
-      <c r="U44" s="211" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>ИТОГО трудоёмкость:</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="21">
-        <f>SUM(E5:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="21">
-        <f>SUM(G5:G44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="32" t="inlineStr">
-        <is>
-          <t>Коэфф. точности оценок (Факт/Оценка):</t>
-        </is>
-      </c>
-      <c r="E47" s="73">
-        <f>IFERROR(SUM(I5:I44)/SUMPRODUCT((I5:I44&lt;&gt;"")*E5:E44),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="38" t="inlineStr">
-        <is>
-          <t>&gt;1 — систематически недооцениваем; множитель для будущих оценок.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="88" t="inlineStr">
-        <is>
-          <t>Средний Cycle time (дн):</t>
-        </is>
-      </c>
-      <c r="E49" s="130">
-        <f>IFERROR(AVERAGEIF(R5:R44,"&gt;=0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="88" t="inlineStr">
-        <is>
-          <t>Средний Lead time (дн):</t>
-        </is>
-      </c>
-      <c r="E50" s="130">
-        <f>IFERROR(AVERAGEIF(S5:S44,"&gt;=0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="D100">
-        <f>E45</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Приоритет" error="Выберите: High, Medium или Low" promptTitle="Приоритет" prompt="Выберите приоритет из списка" type="list">
-      <formula1>"High,Medium,Low"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Статус" error="Выберите: To Do, В работе или Готово" promptTitle="Статус" prompt="Выберите статус из списка" type="list">
-      <formula1>"To Do,В работе,Готово"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K5:K44 N5:N44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Нет,Да"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"1,2,3,4,5,6,7,8,9,10,11"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"История,Задача,Тех.долг"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -38672,6 +36764,2756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15.88671875" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="17"/>
+    <col width="8" customWidth="1" min="18" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Бэклог спринта (задачи)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Оценка (дн) — трудоёмкость задачи в человеко-днях. Остаток пересчитывается по статусу («Готово» → 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27.6" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Исполнитель</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Оценка (дн)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Остаток (дн)</t>
+        </is>
+      </c>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="I4" s="39" t="inlineStr">
+        <is>
+          <t>Факт (дн)</t>
+        </is>
+      </c>
+      <c r="J4" s="39" t="inlineStr">
+        <is>
+          <t>Точность
+(Факт/Оценка)</t>
+        </is>
+      </c>
+      <c r="K4" s="39" t="inlineStr">
+        <is>
+          <t>Блокер</t>
+        </is>
+      </c>
+      <c r="L4" s="39" t="inlineStr">
+        <is>
+          <t>Дней
+в блоке</t>
+        </is>
+      </c>
+      <c r="M4" s="113" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="N4" s="92" t="inlineStr">
+        <is>
+          <t>Добавлено
+после старта</t>
+        </is>
+      </c>
+      <c r="O4" s="92" t="inlineStr">
+        <is>
+          <t>Создана</t>
+        </is>
+      </c>
+      <c r="P4" s="92" t="inlineStr">
+        <is>
+          <t>В работу</t>
+        </is>
+      </c>
+      <c r="Q4" s="92" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="R4" s="92" t="inlineStr">
+        <is>
+          <t>Cycle
+(дн)</t>
+        </is>
+      </c>
+      <c r="S4" s="92" t="inlineStr">
+        <is>
+          <t>Lead
+(дн)</t>
+        </is>
+      </c>
+      <c r="T4" s="92" t="inlineStr">
+        <is>
+          <t>Возраст
+WIP (дн)</t>
+        </is>
+      </c>
+      <c r="U4" s="200" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>T-01</t>
+        </is>
+      </c>
+      <c r="B5" s="95" t="inlineStr">
+        <is>
+          <t>Проектирование API заказов</t>
+        </is>
+      </c>
+      <c r="C5" s="95" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G5" s="23">
+        <f>IF(F5="Готово",0,IF(E5="","",E5))</f>
+        <v/>
+      </c>
+      <c r="H5" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C5,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="97" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="72">
+        <f>IF(AND(I5&lt;&gt;"",E5&lt;&gt;""),I5/E5,"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O5" s="128" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P5" s="128" t="n">
+        <v>46237</v>
+      </c>
+      <c r="Q5" s="128" t="n">
+        <v>46240</v>
+      </c>
+      <c r="R5" s="90">
+        <f>IF(AND(Q5&lt;&gt;"",P5&lt;&gt;""),Q5-P5,"")</f>
+        <v/>
+      </c>
+      <c r="S5" s="90">
+        <f>IF(AND(Q5&lt;&gt;"",O5&lt;&gt;""),Q5-O5,"")</f>
+        <v/>
+      </c>
+      <c r="T5" s="90">
+        <f>IF(AND(F5="В работе",P5&lt;&gt;""),Параметры!$B$10-P5,"")</f>
+        <v/>
+      </c>
+      <c r="U5" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="94" t="inlineStr">
+        <is>
+          <t>T-02</t>
+        </is>
+      </c>
+      <c r="B6" s="95" t="inlineStr">
+        <is>
+          <t>Экран корзины (вёрстка)</t>
+        </is>
+      </c>
+      <c r="C6" s="95" t="inlineStr">
+        <is>
+          <t>Петрова М.</t>
+        </is>
+      </c>
+      <c r="D6" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G6" s="23">
+        <f>IF(F6="Готово",0,IF(E6="","",E6))</f>
+        <v/>
+      </c>
+      <c r="H6" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C6,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="97" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="72">
+        <f>IF(AND(I6&lt;&gt;"",E6&lt;&gt;""),I6/E6,"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O6" s="128" t="n">
+        <v>46233</v>
+      </c>
+      <c r="P6" s="128" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Q6" s="128" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R6" s="90">
+        <f>IF(AND(Q6&lt;&gt;"",P6&lt;&gt;""),Q6-P6,"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="90">
+        <f>IF(AND(Q6&lt;&gt;"",O6&lt;&gt;""),Q6-O6,"")</f>
+        <v/>
+      </c>
+      <c r="T6" s="90">
+        <f>IF(AND(F6="В работе",P6&lt;&gt;""),Параметры!$B$10-P6,"")</f>
+        <v/>
+      </c>
+      <c r="U6" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t>T-09</t>
+        </is>
+      </c>
+      <c r="B7" s="95" t="inlineStr">
+        <is>
+          <t>Настройка CI/CD</t>
+        </is>
+      </c>
+      <c r="C7" s="95" t="inlineStr">
+        <is>
+          <t>Новиков А.</t>
+        </is>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G7" s="23">
+        <f>IF(F7="Готово",0,IF(E7="","",E7))</f>
+        <v/>
+      </c>
+      <c r="H7" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C7,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="72">
+        <f>IF(AND(I7&lt;&gt;"",E7&lt;&gt;""),I7/E7,"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L7" s="33" t="n"/>
+      <c r="M7" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O7" s="128" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P7" s="128" t="n">
+        <v>46237</v>
+      </c>
+      <c r="Q7" s="128" t="n">
+        <v>46239</v>
+      </c>
+      <c r="R7" s="90">
+        <f>IF(AND(Q7&lt;&gt;"",P7&lt;&gt;""),Q7-P7,"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="90">
+        <f>IF(AND(Q7&lt;&gt;"",O7&lt;&gt;""),Q7-O7,"")</f>
+        <v/>
+      </c>
+      <c r="T7" s="90">
+        <f>IF(AND(F7="В работе",P7&lt;&gt;""),Параметры!$B$10-P7,"")</f>
+        <v/>
+      </c>
+      <c r="U7" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
+        <is>
+          <t>Модель данных заказа</t>
+        </is>
+      </c>
+      <c r="C8" s="95" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="D8" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="94" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G8" s="23">
+        <f>IF(F8="Готово",0,IF(E8="","",E8))</f>
+        <v/>
+      </c>
+      <c r="H8" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C8,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="97" t="n"/>
+      <c r="J8" s="72">
+        <f>IF(AND(I8&lt;&gt;"",E8&lt;&gt;""),I8/E8,"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L8" s="33" t="n"/>
+      <c r="M8" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O8" s="128" t="n">
+        <v>46234</v>
+      </c>
+      <c r="P8" s="128" t="n">
+        <v>46239</v>
+      </c>
+      <c r="Q8" s="129" t="n"/>
+      <c r="R8" s="90">
+        <f>IF(AND(Q8&lt;&gt;"",P8&lt;&gt;""),Q8-P8,"")</f>
+        <v/>
+      </c>
+      <c r="S8" s="90">
+        <f>IF(AND(Q8&lt;&gt;"",O8&lt;&gt;""),Q8-O8,"")</f>
+        <v/>
+      </c>
+      <c r="T8" s="90">
+        <f>IF(AND(F8="В работе",P8&lt;&gt;""),Параметры!$B$10-P8,"")</f>
+        <v/>
+      </c>
+      <c r="U8" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="B9" s="95" t="inlineStr">
+        <is>
+          <t>Интеграция платежей</t>
+        </is>
+      </c>
+      <c r="C9" s="95" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="D9" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G9" s="23">
+        <f>IF(F9="Готово",0,IF(E9="","",E9))</f>
+        <v/>
+      </c>
+      <c r="H9" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C9,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="97" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="72">
+        <f>IF(AND(I9&lt;&gt;"",E9&lt;&gt;""),I9/E9,"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L9" s="33" t="n"/>
+      <c r="M9" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O9" s="128" t="n">
+        <v>46244</v>
+      </c>
+      <c r="P9" s="128" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Q9" s="128" t="n">
+        <v>46258</v>
+      </c>
+      <c r="R9" s="90">
+        <f>IF(AND(Q9&lt;&gt;"",P9&lt;&gt;""),Q9-P9,"")</f>
+        <v/>
+      </c>
+      <c r="S9" s="90">
+        <f>IF(AND(Q9&lt;&gt;"",O9&lt;&gt;""),Q9-O9,"")</f>
+        <v/>
+      </c>
+      <c r="T9" s="90">
+        <f>IF(AND(F9="В работе",P9&lt;&gt;""),Параметры!$B$10-P9,"")</f>
+        <v/>
+      </c>
+      <c r="U9" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>Тест-кейсы оформления</t>
+        </is>
+      </c>
+      <c r="C10" s="95" t="inlineStr">
+        <is>
+          <t>Сидоров К.</t>
+        </is>
+      </c>
+      <c r="D10" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G10" s="23">
+        <f>IF(F10="Готово",0,IF(E10="","",E10))</f>
+        <v/>
+      </c>
+      <c r="H10" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C10,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="72">
+        <f>IF(AND(I10&lt;&gt;"",E10&lt;&gt;""),I10/E10,"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L10" s="33" t="n"/>
+      <c r="M10" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O10" s="128" t="n">
+        <v>46246</v>
+      </c>
+      <c r="P10" s="128" t="n">
+        <v>46252</v>
+      </c>
+      <c r="Q10" s="128" t="n">
+        <v>46254</v>
+      </c>
+      <c r="R10" s="90">
+        <f>IF(AND(Q10&lt;&gt;"",P10&lt;&gt;""),Q10-P10,"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="90">
+        <f>IF(AND(Q10&lt;&gt;"",O10&lt;&gt;""),Q10-O10,"")</f>
+        <v/>
+      </c>
+      <c r="T10" s="90">
+        <f>IF(AND(F10="В работе",P10&lt;&gt;""),Параметры!$B$10-P10,"")</f>
+        <v/>
+      </c>
+      <c r="U10" s="201" t="inlineStr">
+        <is>
+          <t>Тех.долг</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>T-08</t>
+        </is>
+      </c>
+      <c r="B11" s="95" t="inlineStr">
+        <is>
+          <t>Уведомления по e-mail</t>
+        </is>
+      </c>
+      <c r="C11" s="95" t="inlineStr">
+        <is>
+          <t>Смирнов П.</t>
+        </is>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E11" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G11" s="23">
+        <f>IF(F11="Готово",0,IF(E11="","",E11))</f>
+        <v/>
+      </c>
+      <c r="H11" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C11,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="72">
+        <f>IF(AND(I11&lt;&gt;"",E11&lt;&gt;""),I11/E11,"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L11" s="33" t="n"/>
+      <c r="M11" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O11" s="128" t="n">
+        <v>46246</v>
+      </c>
+      <c r="P11" s="128" t="n">
+        <v>46253</v>
+      </c>
+      <c r="Q11" s="128" t="n">
+        <v>46260</v>
+      </c>
+      <c r="R11" s="90">
+        <f>IF(AND(Q11&lt;&gt;"",P11&lt;&gt;""),Q11-P11,"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="90">
+        <f>IF(AND(Q11&lt;&gt;"",O11&lt;&gt;""),Q11-O11,"")</f>
+        <v/>
+      </c>
+      <c r="T11" s="90">
+        <f>IF(AND(F11="В работе",P11&lt;&gt;""),Параметры!$B$10-P11,"")</f>
+        <v/>
+      </c>
+      <c r="U11" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>T-11</t>
+        </is>
+      </c>
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>API промокодов</t>
+        </is>
+      </c>
+      <c r="C12" s="95" t="inlineStr">
+        <is>
+          <t>Козлов В.</t>
+        </is>
+      </c>
+      <c r="D12" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="94" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G12" s="23">
+        <f>IF(F12="Готово",0,IF(E12="","",E12))</f>
+        <v/>
+      </c>
+      <c r="H12" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C12,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="72">
+        <f>IF(AND(I12&lt;&gt;"",E12&lt;&gt;""),I12/E12,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L12" s="33" t="n"/>
+      <c r="M12" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O12" s="128" t="n">
+        <v>46245</v>
+      </c>
+      <c r="P12" s="128" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Q12" s="128" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R12" s="90">
+        <f>IF(AND(Q12&lt;&gt;"",P12&lt;&gt;""),Q12-P12,"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="90">
+        <f>IF(AND(Q12&lt;&gt;"",O12&lt;&gt;""),Q12-O12,"")</f>
+        <v/>
+      </c>
+      <c r="T12" s="90">
+        <f>IF(AND(F12="В работе",P12&lt;&gt;""),Параметры!$B$10-P12,"")</f>
+        <v/>
+      </c>
+      <c r="U12" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>T-12</t>
+        </is>
+      </c>
+      <c r="B13" s="95" t="inlineStr">
+        <is>
+          <t>Логирование и метрики</t>
+        </is>
+      </c>
+      <c r="C13" s="95" t="inlineStr">
+        <is>
+          <t>Новиков А.</t>
+        </is>
+      </c>
+      <c r="D13" s="94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G13" s="23">
+        <f>IF(F13="Готово",0,IF(E13="","",E13))</f>
+        <v/>
+      </c>
+      <c r="H13" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C13,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="97" t="n"/>
+      <c r="J13" s="72">
+        <f>IF(AND(I13&lt;&gt;"",E13&lt;&gt;""),I13/E13,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L13" s="33" t="n"/>
+      <c r="M13" s="98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O13" s="129" t="n"/>
+      <c r="P13" s="129" t="n"/>
+      <c r="Q13" s="129" t="n"/>
+      <c r="R13" s="90">
+        <f>IF(AND(Q13&lt;&gt;"",P13&lt;&gt;""),Q13-P13,"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="90">
+        <f>IF(AND(Q13&lt;&gt;"",O13&lt;&gt;""),Q13-O13,"")</f>
+        <v/>
+      </c>
+      <c r="T13" s="90">
+        <f>IF(AND(F13="В работе",P13&lt;&gt;""),Параметры!$B$10-P13,"")</f>
+        <v/>
+      </c>
+      <c r="U13" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>Рефакторинг авторизации</t>
+        </is>
+      </c>
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t>Кузнецов Д.</t>
+        </is>
+      </c>
+      <c r="D14" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="94" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G14" s="23">
+        <f>IF(F14="Готово",0,IF(E14="","",E14))</f>
+        <v/>
+      </c>
+      <c r="H14" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C14,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="97" t="n"/>
+      <c r="J14" s="72">
+        <f>IF(AND(I14&lt;&gt;"",E14&lt;&gt;""),I14/E14,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L14" s="33" t="n"/>
+      <c r="M14" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O14" s="128" t="n">
+        <v>46262</v>
+      </c>
+      <c r="P14" s="128" t="n">
+        <v>46267</v>
+      </c>
+      <c r="Q14" s="129" t="n"/>
+      <c r="R14" s="90">
+        <f>IF(AND(Q14&lt;&gt;"",P14&lt;&gt;""),Q14-P14,"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="90">
+        <f>IF(AND(Q14&lt;&gt;"",O14&lt;&gt;""),Q14-O14,"")</f>
+        <v/>
+      </c>
+      <c r="T14" s="90">
+        <f>IF(AND(F14="В работе",P14&lt;&gt;""),Параметры!$B$10-P14,"")</f>
+        <v/>
+      </c>
+      <c r="U14" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="B15" s="95" t="inlineStr">
+        <is>
+          <t>Аналитика воронки</t>
+        </is>
+      </c>
+      <c r="C15" s="95" t="inlineStr">
+        <is>
+          <t>Орлова Е.</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E15" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G15" s="23">
+        <f>IF(F15="Готово",0,IF(E15="","",E15))</f>
+        <v/>
+      </c>
+      <c r="H15" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C15,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="72">
+        <f>IF(AND(I15&lt;&gt;"",E15&lt;&gt;""),I15/E15,"")</f>
+        <v/>
+      </c>
+      <c r="K15" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L15" s="33" t="n"/>
+      <c r="M15" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="109" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O15" s="129" t="n"/>
+      <c r="P15" s="129" t="n"/>
+      <c r="Q15" s="129" t="n"/>
+      <c r="R15" s="90">
+        <f>IF(AND(Q15&lt;&gt;"",P15&lt;&gt;""),Q15-P15,"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="90">
+        <f>IF(AND(Q15&lt;&gt;"",O15&lt;&gt;""),Q15-O15,"")</f>
+        <v/>
+      </c>
+      <c r="T15" s="90">
+        <f>IF(AND(F15="В работе",P15&lt;&gt;""),Параметры!$B$10-P15,"")</f>
+        <v/>
+      </c>
+      <c r="U15" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="B16" s="95" t="inlineStr">
+        <is>
+          <t>Регресс-тестирование релиза</t>
+        </is>
+      </c>
+      <c r="C16" s="95" t="inlineStr">
+        <is>
+          <t>Сидоров К.</t>
+        </is>
+      </c>
+      <c r="D16" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E16" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G16" s="23">
+        <f>IF(F16="Готово",0,IF(E16="","",E16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C16,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="97" t="n"/>
+      <c r="J16" s="72">
+        <f>IF(AND(I16&lt;&gt;"",E16&lt;&gt;""),I16/E16,"")</f>
+        <v/>
+      </c>
+      <c r="K16" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L16" s="33" t="n"/>
+      <c r="M16" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O16" s="129" t="n"/>
+      <c r="P16" s="129" t="n"/>
+      <c r="Q16" s="129" t="n"/>
+      <c r="R16" s="90">
+        <f>IF(AND(Q16&lt;&gt;"",P16&lt;&gt;""),Q16-P16,"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="90">
+        <f>IF(AND(Q16&lt;&gt;"",O16&lt;&gt;""),Q16-O16,"")</f>
+        <v/>
+      </c>
+      <c r="T16" s="90">
+        <f>IF(AND(F16="В работе",P16&lt;&gt;""),Параметры!$B$10-P16,"")</f>
+        <v/>
+      </c>
+      <c r="U16" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>T-13</t>
+        </is>
+      </c>
+      <c r="B17" s="95" t="inlineStr">
+        <is>
+          <t>Экран оплаты</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="inlineStr">
+        <is>
+          <t>Волкова Н.</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="94" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G17" s="23">
+        <f>IF(F17="Готово",0,IF(E17="","",E17))</f>
+        <v/>
+      </c>
+      <c r="H17" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C17,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="72">
+        <f>IF(AND(I17&lt;&gt;"",E17&lt;&gt;""),I17/E17,"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L17" s="33" t="n"/>
+      <c r="M17" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O17" s="128" t="n">
+        <v>46262</v>
+      </c>
+      <c r="P17" s="128" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Q17" s="129" t="n"/>
+      <c r="R17" s="90">
+        <f>IF(AND(Q17&lt;&gt;"",P17&lt;&gt;""),Q17-P17,"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="90">
+        <f>IF(AND(Q17&lt;&gt;"",O17&lt;&gt;""),Q17-O17,"")</f>
+        <v/>
+      </c>
+      <c r="T17" s="90">
+        <f>IF(AND(F17="В работе",P17&lt;&gt;""),Параметры!$B$10-P17,"")</f>
+        <v/>
+      </c>
+      <c r="U17" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>T-14</t>
+        </is>
+      </c>
+      <c r="B18" s="95" t="inlineStr">
+        <is>
+          <t>Вебхуки платежей</t>
+        </is>
+      </c>
+      <c r="C18" s="95" t="inlineStr">
+        <is>
+          <t>Иванов А.</t>
+        </is>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G18" s="23">
+        <f>IF(F18="Готово",0,IF(E18="","",E18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C18,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="97" t="n"/>
+      <c r="J18" s="72">
+        <f>IF(AND(I18&lt;&gt;"",E18&lt;&gt;""),I18/E18,"")</f>
+        <v/>
+      </c>
+      <c r="K18" s="99" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L18" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="109" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O18" s="129" t="n"/>
+      <c r="P18" s="129" t="n"/>
+      <c r="Q18" s="129" t="n"/>
+      <c r="R18" s="90">
+        <f>IF(AND(Q18&lt;&gt;"",P18&lt;&gt;""),Q18-P18,"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="90">
+        <f>IF(AND(Q18&lt;&gt;"",O18&lt;&gt;""),Q18-O18,"")</f>
+        <v/>
+      </c>
+      <c r="T18" s="90">
+        <f>IF(AND(F18="В работе",P18&lt;&gt;""),Параметры!$B$10-P18,"")</f>
+        <v/>
+      </c>
+      <c r="U18" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>T-15</t>
+        </is>
+      </c>
+      <c r="B19" s="95" t="inlineStr">
+        <is>
+          <t>История заказов</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="inlineStr">
+        <is>
+          <t>Соколов Р.</t>
+        </is>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G19" s="23">
+        <f>IF(F19="Готово",0,IF(E19="","",E19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C19,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="72">
+        <f>IF(AND(I19&lt;&gt;"",E19&lt;&gt;""),I19/E19,"")</f>
+        <v/>
+      </c>
+      <c r="K19" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L19" s="33" t="n"/>
+      <c r="M19" s="98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O19" s="129" t="n"/>
+      <c r="P19" s="129" t="n"/>
+      <c r="Q19" s="129" t="n"/>
+      <c r="R19" s="90">
+        <f>IF(AND(Q19&lt;&gt;"",P19&lt;&gt;""),Q19-P19,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="90">
+        <f>IF(AND(Q19&lt;&gt;"",O19&lt;&gt;""),Q19-O19,"")</f>
+        <v/>
+      </c>
+      <c r="T19" s="90">
+        <f>IF(AND(F19="В работе",P19&lt;&gt;""),Параметры!$B$10-P19,"")</f>
+        <v/>
+      </c>
+      <c r="U19" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>T-16</t>
+        </is>
+      </c>
+      <c r="B20" s="95" t="inlineStr">
+        <is>
+          <t>Личный кабинет</t>
+        </is>
+      </c>
+      <c r="C20" s="95" t="inlineStr">
+        <is>
+          <t>Волкова Н.</t>
+        </is>
+      </c>
+      <c r="D20" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G20" s="23">
+        <f>IF(F20="Готово",0,IF(E20="","",E20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C20,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="97" t="n"/>
+      <c r="J20" s="72">
+        <f>IF(AND(I20&lt;&gt;"",E20&lt;&gt;""),I20/E20,"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="98" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O20" s="129" t="n"/>
+      <c r="P20" s="129" t="n"/>
+      <c r="Q20" s="129" t="n"/>
+      <c r="R20" s="90">
+        <f>IF(AND(Q20&lt;&gt;"",P20&lt;&gt;""),Q20-P20,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="90">
+        <f>IF(AND(Q20&lt;&gt;"",O20&lt;&gt;""),Q20-O20,"")</f>
+        <v/>
+      </c>
+      <c r="T20" s="90">
+        <f>IF(AND(F20="В работе",P20&lt;&gt;""),Параметры!$B$10-P20,"")</f>
+        <v/>
+      </c>
+      <c r="U20" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>T-17</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>Фильтры каталога</t>
+        </is>
+      </c>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>Морозов И.</t>
+        </is>
+      </c>
+      <c r="D21" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G21" s="23">
+        <f>IF(F21="Готово",0,IF(E21="","",E21))</f>
+        <v/>
+      </c>
+      <c r="H21" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C21,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="97" t="n"/>
+      <c r="J21" s="72">
+        <f>IF(AND(I21&lt;&gt;"",E21&lt;&gt;""),I21/E21,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="98" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O21" s="129" t="n"/>
+      <c r="P21" s="129" t="n"/>
+      <c r="Q21" s="129" t="n"/>
+      <c r="R21" s="90">
+        <f>IF(AND(Q21&lt;&gt;"",P21&lt;&gt;""),Q21-P21,"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="90">
+        <f>IF(AND(Q21&lt;&gt;"",O21&lt;&gt;""),Q21-O21,"")</f>
+        <v/>
+      </c>
+      <c r="T21" s="90">
+        <f>IF(AND(F21="В работе",P21&lt;&gt;""),Параметры!$B$10-P21,"")</f>
+        <v/>
+      </c>
+      <c r="U21" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>T-18</t>
+        </is>
+      </c>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>Отзывы и рейтинги</t>
+        </is>
+      </c>
+      <c r="C22" s="95" t="inlineStr">
+        <is>
+          <t>Лебедева Т.</t>
+        </is>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E22" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G22" s="23">
+        <f>IF(F22="Готово",0,IF(E22="","",E22))</f>
+        <v/>
+      </c>
+      <c r="H22" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C22,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="97" t="n"/>
+      <c r="J22" s="72">
+        <f>IF(AND(I22&lt;&gt;"",E22&lt;&gt;""),I22/E22,"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="98" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O22" s="129" t="n"/>
+      <c r="P22" s="129" t="n"/>
+      <c r="Q22" s="129" t="n"/>
+      <c r="R22" s="90">
+        <f>IF(AND(Q22&lt;&gt;"",P22&lt;&gt;""),Q22-P22,"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="90">
+        <f>IF(AND(Q22&lt;&gt;"",O22&lt;&gt;""),Q22-O22,"")</f>
+        <v/>
+      </c>
+      <c r="T22" s="90">
+        <f>IF(AND(F22="В работе",P22&lt;&gt;""),Параметры!$B$10-P22,"")</f>
+        <v/>
+      </c>
+      <c r="U22" s="201" t="inlineStr">
+        <is>
+          <t>Тех.долг</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>T-19</t>
+        </is>
+      </c>
+      <c r="B23" s="95" t="inlineStr">
+        <is>
+          <t>Рекомендации</t>
+        </is>
+      </c>
+      <c r="C23" s="95" t="inlineStr">
+        <is>
+          <t>Фёдорова О.</t>
+        </is>
+      </c>
+      <c r="D23" s="94" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E23" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G23" s="23">
+        <f>IF(F23="Готово",0,IF(E23="","",E23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C23,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="97" t="n"/>
+      <c r="J23" s="72">
+        <f>IF(AND(I23&lt;&gt;"",E23&lt;&gt;""),I23/E23,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L23" s="33" t="n"/>
+      <c r="M23" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O23" s="129" t="n"/>
+      <c r="P23" s="129" t="n"/>
+      <c r="Q23" s="129" t="n"/>
+      <c r="R23" s="90">
+        <f>IF(AND(Q23&lt;&gt;"",P23&lt;&gt;""),Q23-P23,"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="90">
+        <f>IF(AND(Q23&lt;&gt;"",O23&lt;&gt;""),Q23-O23,"")</f>
+        <v/>
+      </c>
+      <c r="T23" s="90">
+        <f>IF(AND(F23="В работе",P23&lt;&gt;""),Параметры!$B$10-P23,"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="201" t="inlineStr">
+        <is>
+          <t>История</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>T-20</t>
+        </is>
+      </c>
+      <c r="B24" s="95" t="inlineStr">
+        <is>
+          <t>A/B тесты чекаута</t>
+        </is>
+      </c>
+      <c r="C24" s="95" t="inlineStr">
+        <is>
+          <t>Морозов И.</t>
+        </is>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E24" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="94" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="G24" s="23">
+        <f>IF(F24="Готово",0,IF(E24="","",E24))</f>
+        <v/>
+      </c>
+      <c r="H24" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C24,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="97" t="n"/>
+      <c r="J24" s="72">
+        <f>IF(AND(I24&lt;&gt;"",E24&lt;&gt;""),I24/E24,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="98" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O24" s="129" t="n"/>
+      <c r="P24" s="129" t="n"/>
+      <c r="Q24" s="129" t="n"/>
+      <c r="R24" s="90">
+        <f>IF(AND(Q24&lt;&gt;"",P24&lt;&gt;""),Q24-P24,"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="90">
+        <f>IF(AND(Q24&lt;&gt;"",O24&lt;&gt;""),Q24-O24,"")</f>
+        <v/>
+      </c>
+      <c r="T24" s="90">
+        <f>IF(AND(F24="В работе",P24&lt;&gt;""),Параметры!$B$10-P24,"")</f>
+        <v/>
+      </c>
+      <c r="U24" s="201" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="23">
+        <f>IF(F25="Готово",0,IF(E25="","",E25))</f>
+        <v/>
+      </c>
+      <c r="H25" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C25,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="71" t="n"/>
+      <c r="J25" s="72">
+        <f>IF(AND(I25&lt;&gt;"",E25&lt;&gt;""),I25/E25,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L25" s="33" t="n"/>
+      <c r="M25" s="101" t="n"/>
+      <c r="N25" s="109" t="n"/>
+      <c r="O25" s="129" t="n"/>
+      <c r="P25" s="129" t="n"/>
+      <c r="Q25" s="129" t="n"/>
+      <c r="R25" s="90">
+        <f>IF(AND(Q25&lt;&gt;"",P25&lt;&gt;""),Q25-P25,"")</f>
+        <v/>
+      </c>
+      <c r="S25" s="90">
+        <f>IF(AND(Q25&lt;&gt;"",O25&lt;&gt;""),Q25-O25,"")</f>
+        <v/>
+      </c>
+      <c r="T25" s="90">
+        <f>IF(AND(F25="В работе",P25&lt;&gt;""),Параметры!$B$10-P25,"")</f>
+        <v/>
+      </c>
+      <c r="U25" s="211" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="23">
+        <f>IF(F26="Готово",0,IF(E26="","",E26))</f>
+        <v/>
+      </c>
+      <c r="H26" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C26,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="71" t="n"/>
+      <c r="J26" s="72">
+        <f>IF(AND(I26&lt;&gt;"",E26&lt;&gt;""),I26/E26,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="101" t="n"/>
+      <c r="N26" s="109" t="n"/>
+      <c r="O26" s="129" t="n"/>
+      <c r="P26" s="129" t="n"/>
+      <c r="Q26" s="129" t="n"/>
+      <c r="R26" s="90">
+        <f>IF(AND(Q26&lt;&gt;"",P26&lt;&gt;""),Q26-P26,"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="90">
+        <f>IF(AND(Q26&lt;&gt;"",O26&lt;&gt;""),Q26-O26,"")</f>
+        <v/>
+      </c>
+      <c r="T26" s="90">
+        <f>IF(AND(F26="В работе",P26&lt;&gt;""),Параметры!$B$10-P26,"")</f>
+        <v/>
+      </c>
+      <c r="U26" s="211" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="23">
+        <f>IF(F27="Готово",0,IF(E27="","",E27))</f>
+        <v/>
+      </c>
+      <c r="H27" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C27,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="71" t="n"/>
+      <c r="J27" s="72">
+        <f>IF(AND(I27&lt;&gt;"",E27&lt;&gt;""),I27/E27,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L27" s="33" t="n"/>
+      <c r="M27" s="101" t="n"/>
+      <c r="N27" s="109" t="n"/>
+      <c r="O27" s="129" t="n"/>
+      <c r="P27" s="129" t="n"/>
+      <c r="Q27" s="129" t="n"/>
+      <c r="R27" s="90">
+        <f>IF(AND(Q27&lt;&gt;"",P27&lt;&gt;""),Q27-P27,"")</f>
+        <v/>
+      </c>
+      <c r="S27" s="90">
+        <f>IF(AND(Q27&lt;&gt;"",O27&lt;&gt;""),Q27-O27,"")</f>
+        <v/>
+      </c>
+      <c r="T27" s="90">
+        <f>IF(AND(F27="В работе",P27&lt;&gt;""),Параметры!$B$10-P27,"")</f>
+        <v/>
+      </c>
+      <c r="U27" s="211" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="23">
+        <f>IF(F28="Готово",0,IF(E28="","",E28))</f>
+        <v/>
+      </c>
+      <c r="H28" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C28,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="71" t="n"/>
+      <c r="J28" s="72">
+        <f>IF(AND(I28&lt;&gt;"",E28&lt;&gt;""),I28/E28,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="101" t="n"/>
+      <c r="N28" s="109" t="n"/>
+      <c r="O28" s="129" t="n"/>
+      <c r="P28" s="129" t="n"/>
+      <c r="Q28" s="129" t="n"/>
+      <c r="R28" s="90">
+        <f>IF(AND(Q28&lt;&gt;"",P28&lt;&gt;""),Q28-P28,"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="90">
+        <f>IF(AND(Q28&lt;&gt;"",O28&lt;&gt;""),Q28-O28,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="90">
+        <f>IF(AND(F28="В работе",P28&lt;&gt;""),Параметры!$B$10-P28,"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="211" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="23">
+        <f>IF(F29="Готово",0,IF(E29="","",E29))</f>
+        <v/>
+      </c>
+      <c r="H29" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C29,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="71" t="n"/>
+      <c r="J29" s="72">
+        <f>IF(AND(I29&lt;&gt;"",E29&lt;&gt;""),I29/E29,"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L29" s="33" t="n"/>
+      <c r="M29" s="101" t="n"/>
+      <c r="N29" s="109" t="n"/>
+      <c r="O29" s="129" t="n"/>
+      <c r="P29" s="129" t="n"/>
+      <c r="Q29" s="129" t="n"/>
+      <c r="R29" s="90">
+        <f>IF(AND(Q29&lt;&gt;"",P29&lt;&gt;""),Q29-P29,"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="90">
+        <f>IF(AND(Q29&lt;&gt;"",O29&lt;&gt;""),Q29-O29,"")</f>
+        <v/>
+      </c>
+      <c r="T29" s="90">
+        <f>IF(AND(F29="В работе",P29&lt;&gt;""),Параметры!$B$10-P29,"")</f>
+        <v/>
+      </c>
+      <c r="U29" s="211" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="23">
+        <f>IF(F30="Готово",0,IF(E30="","",E30))</f>
+        <v/>
+      </c>
+      <c r="H30" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C30,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="71" t="n"/>
+      <c r="J30" s="72">
+        <f>IF(AND(I30&lt;&gt;"",E30&lt;&gt;""),I30/E30,"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="101" t="n"/>
+      <c r="N30" s="109" t="n"/>
+      <c r="O30" s="129" t="n"/>
+      <c r="P30" s="129" t="n"/>
+      <c r="Q30" s="129" t="n"/>
+      <c r="R30" s="90">
+        <f>IF(AND(Q30&lt;&gt;"",P30&lt;&gt;""),Q30-P30,"")</f>
+        <v/>
+      </c>
+      <c r="S30" s="90">
+        <f>IF(AND(Q30&lt;&gt;"",O30&lt;&gt;""),Q30-O30,"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="90">
+        <f>IF(AND(F30="В работе",P30&lt;&gt;""),Параметры!$B$10-P30,"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="211" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="23">
+        <f>IF(F31="Готово",0,IF(E31="","",E31))</f>
+        <v/>
+      </c>
+      <c r="H31" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C31,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="71" t="n"/>
+      <c r="J31" s="72">
+        <f>IF(AND(I31&lt;&gt;"",E31&lt;&gt;""),I31/E31,"")</f>
+        <v/>
+      </c>
+      <c r="K31" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L31" s="33" t="n"/>
+      <c r="M31" s="101" t="n"/>
+      <c r="N31" s="109" t="n"/>
+      <c r="O31" s="129" t="n"/>
+      <c r="P31" s="129" t="n"/>
+      <c r="Q31" s="129" t="n"/>
+      <c r="R31" s="90">
+        <f>IF(AND(Q31&lt;&gt;"",P31&lt;&gt;""),Q31-P31,"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="90">
+        <f>IF(AND(Q31&lt;&gt;"",O31&lt;&gt;""),Q31-O31,"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="90">
+        <f>IF(AND(F31="В работе",P31&lt;&gt;""),Параметры!$B$10-P31,"")</f>
+        <v/>
+      </c>
+      <c r="U31" s="211" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="23">
+        <f>IF(F32="Готово",0,IF(E32="","",E32))</f>
+        <v/>
+      </c>
+      <c r="H32" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C32,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="71" t="n"/>
+      <c r="J32" s="72">
+        <f>IF(AND(I32&lt;&gt;"",E32&lt;&gt;""),I32/E32,"")</f>
+        <v/>
+      </c>
+      <c r="K32" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="101" t="n"/>
+      <c r="N32" s="109" t="n"/>
+      <c r="O32" s="129" t="n"/>
+      <c r="P32" s="129" t="n"/>
+      <c r="Q32" s="129" t="n"/>
+      <c r="R32" s="90">
+        <f>IF(AND(Q32&lt;&gt;"",P32&lt;&gt;""),Q32-P32,"")</f>
+        <v/>
+      </c>
+      <c r="S32" s="90">
+        <f>IF(AND(Q32&lt;&gt;"",O32&lt;&gt;""),Q32-O32,"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="90">
+        <f>IF(AND(F32="В работе",P32&lt;&gt;""),Параметры!$B$10-P32,"")</f>
+        <v/>
+      </c>
+      <c r="U32" s="211" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="23">
+        <f>IF(F33="Готово",0,IF(E33="","",E33))</f>
+        <v/>
+      </c>
+      <c r="H33" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C33,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="71" t="n"/>
+      <c r="J33" s="72">
+        <f>IF(AND(I33&lt;&gt;"",E33&lt;&gt;""),I33/E33,"")</f>
+        <v/>
+      </c>
+      <c r="K33" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L33" s="33" t="n"/>
+      <c r="M33" s="101" t="n"/>
+      <c r="N33" s="109" t="n"/>
+      <c r="O33" s="129" t="n"/>
+      <c r="P33" s="129" t="n"/>
+      <c r="Q33" s="129" t="n"/>
+      <c r="R33" s="90">
+        <f>IF(AND(Q33&lt;&gt;"",P33&lt;&gt;""),Q33-P33,"")</f>
+        <v/>
+      </c>
+      <c r="S33" s="90">
+        <f>IF(AND(Q33&lt;&gt;"",O33&lt;&gt;""),Q33-O33,"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="90">
+        <f>IF(AND(F33="В работе",P33&lt;&gt;""),Параметры!$B$10-P33,"")</f>
+        <v/>
+      </c>
+      <c r="U33" s="211" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="23">
+        <f>IF(F34="Готово",0,IF(E34="","",E34))</f>
+        <v/>
+      </c>
+      <c r="H34" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C34,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="71" t="n"/>
+      <c r="J34" s="72">
+        <f>IF(AND(I34&lt;&gt;"",E34&lt;&gt;""),I34/E34,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="101" t="n"/>
+      <c r="N34" s="109" t="n"/>
+      <c r="O34" s="129" t="n"/>
+      <c r="P34" s="129" t="n"/>
+      <c r="Q34" s="129" t="n"/>
+      <c r="R34" s="90">
+        <f>IF(AND(Q34&lt;&gt;"",P34&lt;&gt;""),Q34-P34,"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="90">
+        <f>IF(AND(Q34&lt;&gt;"",O34&lt;&gt;""),Q34-O34,"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="90">
+        <f>IF(AND(F34="В работе",P34&lt;&gt;""),Параметры!$B$10-P34,"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="211" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="23">
+        <f>IF(F35="Готово",0,IF(E35="","",E35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C35,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="71" t="n"/>
+      <c r="J35" s="72">
+        <f>IF(AND(I35&lt;&gt;"",E35&lt;&gt;""),I35/E35,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L35" s="33" t="n"/>
+      <c r="M35" s="101" t="n"/>
+      <c r="N35" s="109" t="n"/>
+      <c r="O35" s="129" t="n"/>
+      <c r="P35" s="129" t="n"/>
+      <c r="Q35" s="129" t="n"/>
+      <c r="R35" s="90">
+        <f>IF(AND(Q35&lt;&gt;"",P35&lt;&gt;""),Q35-P35,"")</f>
+        <v/>
+      </c>
+      <c r="S35" s="90">
+        <f>IF(AND(Q35&lt;&gt;"",O35&lt;&gt;""),Q35-O35,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="90">
+        <f>IF(AND(F35="В работе",P35&lt;&gt;""),Параметры!$B$10-P35,"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="211" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="24" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="23">
+        <f>IF(F36="Готово",0,IF(E36="","",E36))</f>
+        <v/>
+      </c>
+      <c r="H36" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C36,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="71" t="n"/>
+      <c r="J36" s="72">
+        <f>IF(AND(I36&lt;&gt;"",E36&lt;&gt;""),I36/E36,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="101" t="n"/>
+      <c r="N36" s="109" t="n"/>
+      <c r="O36" s="129" t="n"/>
+      <c r="P36" s="129" t="n"/>
+      <c r="Q36" s="129" t="n"/>
+      <c r="R36" s="90">
+        <f>IF(AND(Q36&lt;&gt;"",P36&lt;&gt;""),Q36-P36,"")</f>
+        <v/>
+      </c>
+      <c r="S36" s="90">
+        <f>IF(AND(Q36&lt;&gt;"",O36&lt;&gt;""),Q36-O36,"")</f>
+        <v/>
+      </c>
+      <c r="T36" s="90">
+        <f>IF(AND(F36="В работе",P36&lt;&gt;""),Параметры!$B$10-P36,"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="211" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="23">
+        <f>IF(F37="Готово",0,IF(E37="","",E37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C37,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="71" t="n"/>
+      <c r="J37" s="72">
+        <f>IF(AND(I37&lt;&gt;"",E37&lt;&gt;""),I37/E37,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L37" s="33" t="n"/>
+      <c r="M37" s="101" t="n"/>
+      <c r="N37" s="109" t="n"/>
+      <c r="O37" s="129" t="n"/>
+      <c r="P37" s="129" t="n"/>
+      <c r="Q37" s="129" t="n"/>
+      <c r="R37" s="90">
+        <f>IF(AND(Q37&lt;&gt;"",P37&lt;&gt;""),Q37-P37,"")</f>
+        <v/>
+      </c>
+      <c r="S37" s="90">
+        <f>IF(AND(Q37&lt;&gt;"",O37&lt;&gt;""),Q37-O37,"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="90">
+        <f>IF(AND(F37="В работе",P37&lt;&gt;""),Параметры!$B$10-P37,"")</f>
+        <v/>
+      </c>
+      <c r="U37" s="211" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="23">
+        <f>IF(F38="Готово",0,IF(E38="","",E38))</f>
+        <v/>
+      </c>
+      <c r="H38" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C38,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="71" t="n"/>
+      <c r="J38" s="72">
+        <f>IF(AND(I38&lt;&gt;"",E38&lt;&gt;""),I38/E38,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="101" t="n"/>
+      <c r="N38" s="109" t="n"/>
+      <c r="O38" s="129" t="n"/>
+      <c r="P38" s="129" t="n"/>
+      <c r="Q38" s="129" t="n"/>
+      <c r="R38" s="90">
+        <f>IF(AND(Q38&lt;&gt;"",P38&lt;&gt;""),Q38-P38,"")</f>
+        <v/>
+      </c>
+      <c r="S38" s="90">
+        <f>IF(AND(Q38&lt;&gt;"",O38&lt;&gt;""),Q38-O38,"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="90">
+        <f>IF(AND(F38="В работе",P38&lt;&gt;""),Параметры!$B$10-P38,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="211" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="23">
+        <f>IF(F39="Готово",0,IF(E39="","",E39))</f>
+        <v/>
+      </c>
+      <c r="H39" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C39,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="71" t="n"/>
+      <c r="J39" s="72">
+        <f>IF(AND(I39&lt;&gt;"",E39&lt;&gt;""),I39/E39,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L39" s="33" t="n"/>
+      <c r="M39" s="101" t="n"/>
+      <c r="N39" s="109" t="n"/>
+      <c r="O39" s="129" t="n"/>
+      <c r="P39" s="129" t="n"/>
+      <c r="Q39" s="129" t="n"/>
+      <c r="R39" s="90">
+        <f>IF(AND(Q39&lt;&gt;"",P39&lt;&gt;""),Q39-P39,"")</f>
+        <v/>
+      </c>
+      <c r="S39" s="90">
+        <f>IF(AND(Q39&lt;&gt;"",O39&lt;&gt;""),Q39-O39,"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="90">
+        <f>IF(AND(F39="В работе",P39&lt;&gt;""),Параметры!$B$10-P39,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="211" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="23">
+        <f>IF(F40="Готово",0,IF(E40="","",E40))</f>
+        <v/>
+      </c>
+      <c r="H40" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C40,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="71" t="n"/>
+      <c r="J40" s="72">
+        <f>IF(AND(I40&lt;&gt;"",E40&lt;&gt;""),I40/E40,"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L40" s="33" t="n"/>
+      <c r="M40" s="101" t="n"/>
+      <c r="N40" s="109" t="n"/>
+      <c r="O40" s="129" t="n"/>
+      <c r="P40" s="129" t="n"/>
+      <c r="Q40" s="129" t="n"/>
+      <c r="R40" s="90">
+        <f>IF(AND(Q40&lt;&gt;"",P40&lt;&gt;""),Q40-P40,"")</f>
+        <v/>
+      </c>
+      <c r="S40" s="90">
+        <f>IF(AND(Q40&lt;&gt;"",O40&lt;&gt;""),Q40-O40,"")</f>
+        <v/>
+      </c>
+      <c r="T40" s="90">
+        <f>IF(AND(F40="В работе",P40&lt;&gt;""),Параметры!$B$10-P40,"")</f>
+        <v/>
+      </c>
+      <c r="U40" s="211" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="23">
+        <f>IF(F41="Готово",0,IF(E41="","",E41))</f>
+        <v/>
+      </c>
+      <c r="H41" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C41,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="71" t="n"/>
+      <c r="J41" s="72">
+        <f>IF(AND(I41&lt;&gt;"",E41&lt;&gt;""),I41/E41,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L41" s="33" t="n"/>
+      <c r="M41" s="101" t="n"/>
+      <c r="N41" s="109" t="n"/>
+      <c r="O41" s="129" t="n"/>
+      <c r="P41" s="129" t="n"/>
+      <c r="Q41" s="129" t="n"/>
+      <c r="R41" s="90">
+        <f>IF(AND(Q41&lt;&gt;"",P41&lt;&gt;""),Q41-P41,"")</f>
+        <v/>
+      </c>
+      <c r="S41" s="90">
+        <f>IF(AND(Q41&lt;&gt;"",O41&lt;&gt;""),Q41-O41,"")</f>
+        <v/>
+      </c>
+      <c r="T41" s="90">
+        <f>IF(AND(F41="В работе",P41&lt;&gt;""),Параметры!$B$10-P41,"")</f>
+        <v/>
+      </c>
+      <c r="U41" s="211" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="23">
+        <f>IF(F42="Готово",0,IF(E42="","",E42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C42,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="71" t="n"/>
+      <c r="J42" s="72">
+        <f>IF(AND(I42&lt;&gt;"",E42&lt;&gt;""),I42/E42,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L42" s="33" t="n"/>
+      <c r="M42" s="101" t="n"/>
+      <c r="N42" s="109" t="n"/>
+      <c r="O42" s="129" t="n"/>
+      <c r="P42" s="129" t="n"/>
+      <c r="Q42" s="129" t="n"/>
+      <c r="R42" s="90">
+        <f>IF(AND(Q42&lt;&gt;"",P42&lt;&gt;""),Q42-P42,"")</f>
+        <v/>
+      </c>
+      <c r="S42" s="90">
+        <f>IF(AND(Q42&lt;&gt;"",O42&lt;&gt;""),Q42-O42,"")</f>
+        <v/>
+      </c>
+      <c r="T42" s="90">
+        <f>IF(AND(F42="В работе",P42&lt;&gt;""),Параметры!$B$10-P42,"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="211" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="23">
+        <f>IF(F43="Готово",0,IF(E43="","",E43))</f>
+        <v/>
+      </c>
+      <c r="H43" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C43,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="71" t="n"/>
+      <c r="J43" s="72">
+        <f>IF(AND(I43&lt;&gt;"",E43&lt;&gt;""),I43/E43,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L43" s="33" t="n"/>
+      <c r="M43" s="101" t="n"/>
+      <c r="N43" s="109" t="n"/>
+      <c r="O43" s="129" t="n"/>
+      <c r="P43" s="129" t="n"/>
+      <c r="Q43" s="129" t="n"/>
+      <c r="R43" s="90">
+        <f>IF(AND(Q43&lt;&gt;"",P43&lt;&gt;""),Q43-P43,"")</f>
+        <v/>
+      </c>
+      <c r="S43" s="90">
+        <f>IF(AND(Q43&lt;&gt;"",O43&lt;&gt;""),Q43-O43,"")</f>
+        <v/>
+      </c>
+      <c r="T43" s="90">
+        <f>IF(AND(F43="В работе",P43&lt;&gt;""),Параметры!$B$10-P43,"")</f>
+        <v/>
+      </c>
+      <c r="U43" s="211" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="23">
+        <f>IF(F44="Готово",0,IF(E44="","",E44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="70">
+        <f>IFERROR(INDEX(Капасити!$C$5:$C$147,MATCH($C44,Капасити!$B$5:$B$147,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="71" t="n"/>
+      <c r="J44" s="72">
+        <f>IF(AND(I44&lt;&gt;"",E44&lt;&gt;""),I44/E44,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="50" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L44" s="33" t="n"/>
+      <c r="M44" s="101" t="n"/>
+      <c r="N44" s="109" t="n"/>
+      <c r="O44" s="129" t="n"/>
+      <c r="P44" s="129" t="n"/>
+      <c r="Q44" s="129" t="n"/>
+      <c r="R44" s="90">
+        <f>IF(AND(Q44&lt;&gt;"",P44&lt;&gt;""),Q44-P44,"")</f>
+        <v/>
+      </c>
+      <c r="S44" s="90">
+        <f>IF(AND(Q44&lt;&gt;"",O44&lt;&gt;""),Q44-O44,"")</f>
+        <v/>
+      </c>
+      <c r="T44" s="90">
+        <f>IF(AND(F44="В работе",P44&lt;&gt;""),Параметры!$B$10-P44,"")</f>
+        <v/>
+      </c>
+      <c r="U44" s="211" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>ИТОГО трудоёмкость:</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="21">
+        <f>SUM(E5:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="21">
+        <f>SUM(G5:G44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>Коэфф. точности оценок (Факт/Оценка):</t>
+        </is>
+      </c>
+      <c r="E47" s="73">
+        <f>IFERROR(SUM(I5:I44)/SUMPRODUCT((I5:I44&lt;&gt;"")*E5:E44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="38" t="inlineStr">
+        <is>
+          <t>&gt;1 — систематически недооцениваем; множитель для будущих оценок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="88" t="inlineStr">
+        <is>
+          <t>Средний Cycle time (дн):</t>
+        </is>
+      </c>
+      <c r="E49" s="130">
+        <f>IFERROR(AVERAGEIF(R5:R44,"&gt;=0"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="88" t="inlineStr">
+        <is>
+          <t>Средний Lead time (дн):</t>
+        </is>
+      </c>
+      <c r="E50" s="130">
+        <f>IFERROR(AVERAGEIF(S5:S44,"&gt;=0"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="D100">
+        <f>E45</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Приоритет" error="Выберите: High, Medium или Low" promptTitle="Приоритет" prompt="Выберите приоритет из списка" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Статус" error="Выберите: To Do, В работе или Готово" promptTitle="Статус" prompt="Выберите статус из списка" type="list">
+      <formula1>"To Do,В работе,Готово"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K5:K44 N5:N44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Нет,Да"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,11"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"История,Задача,Тех.долг"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -39108,7 +39950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39648,7 +40490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41204,7 +42046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41501,7 +42343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42247,7 +43089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42878,7 +43720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43139,7 +43981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43553,7 +44395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44043,615 +44885,6 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="5"/>
-    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="213" t="inlineStr">
-        <is>
-          <t>Time to Market (TTM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="214" t="inlineStr">
-        <is>
-          <t>TTM = дата релиза − дата взятия задачи в работу. Цель — 15 дней.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Цель TTM (дн):</t>
-        </is>
-      </c>
-      <c r="C3" s="215" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Средний TTM (дн):</t>
-        </is>
-      </c>
-      <c r="C4" s="216">
-        <f>IFERROR(AVERAGEIF(D7:D26,"&gt;=0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="27.6" customHeight="1">
-      <c r="A6" s="217" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-      <c r="B6" s="217" t="inlineStr">
-        <is>
-          <t>В работу</t>
-        </is>
-      </c>
-      <c r="C6" s="217" t="inlineStr">
-        <is>
-          <t>Дата релиза</t>
-        </is>
-      </c>
-      <c r="D6" s="217" t="inlineStr">
-        <is>
-          <t>TTM (дн)</t>
-        </is>
-      </c>
-      <c r="E6" s="217" t="inlineStr">
-        <is>
-          <t>Цель (дн)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TTM (дн)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="218">
-        <f>IF(Бэклог!A5="","",Бэклог!A5)</f>
-        <v/>
-      </c>
-      <c r="B7" s="219">
-        <f>IF(Бэклог!P5="","",Бэклог!P5)</f>
-        <v/>
-      </c>
-      <c r="C7" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M5)*(Релизы!$D$5:$D$9&gt;=Бэклог!M5)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="220">
-        <f>IF(AND(B7&lt;&gt;"",C7&gt;0),C7-B7,"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="186">
-        <f>IF(D7="",NA(),D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="218">
-        <f>IF(Бэклог!A6="","",Бэклог!A6)</f>
-        <v/>
-      </c>
-      <c r="B8" s="219">
-        <f>IF(Бэклог!P6="","",Бэклог!P6)</f>
-        <v/>
-      </c>
-      <c r="C8" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M6)*(Релизы!$D$5:$D$9&gt;=Бэклог!M6)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="220">
-        <f>IF(AND(B8&lt;&gt;"",C8&gt;0),C8-B8,"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="186">
-        <f>IF(D8="",NA(),D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="218">
-        <f>IF(Бэклог!A7="","",Бэклог!A7)</f>
-        <v/>
-      </c>
-      <c r="B9" s="219">
-        <f>IF(Бэклог!P7="","",Бэклог!P7)</f>
-        <v/>
-      </c>
-      <c r="C9" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M7)*(Релизы!$D$5:$D$9&gt;=Бэклог!M7)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="220">
-        <f>IF(AND(B9&lt;&gt;"",C9&gt;0),C9-B9,"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="186">
-        <f>IF(D9="",NA(),D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="218">
-        <f>IF(Бэклог!A8="","",Бэклог!A8)</f>
-        <v/>
-      </c>
-      <c r="B10" s="219">
-        <f>IF(Бэклог!P8="","",Бэклог!P8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M8)*(Релизы!$D$5:$D$9&gt;=Бэклог!M8)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="220">
-        <f>IF(AND(B10&lt;&gt;"",C10&gt;0),C10-B10,"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="186">
-        <f>IF(D10="",NA(),D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="218">
-        <f>IF(Бэклог!A9="","",Бэклог!A9)</f>
-        <v/>
-      </c>
-      <c r="B11" s="219">
-        <f>IF(Бэклог!P9="","",Бэклог!P9)</f>
-        <v/>
-      </c>
-      <c r="C11" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M9)*(Релизы!$D$5:$D$9&gt;=Бэклог!M9)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="220">
-        <f>IF(AND(B11&lt;&gt;"",C11&gt;0),C11-B11,"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="186">
-        <f>IF(D11="",NA(),D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="218">
-        <f>IF(Бэклог!A10="","",Бэклог!A10)</f>
-        <v/>
-      </c>
-      <c r="B12" s="219">
-        <f>IF(Бэклог!P10="","",Бэклог!P10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M10)*(Релизы!$D$5:$D$9&gt;=Бэклог!M10)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="220">
-        <f>IF(AND(B12&lt;&gt;"",C12&gt;0),C12-B12,"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="186">
-        <f>IF(D12="",NA(),D12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="218">
-        <f>IF(Бэклог!A11="","",Бэклог!A11)</f>
-        <v/>
-      </c>
-      <c r="B13" s="219">
-        <f>IF(Бэклог!P11="","",Бэклог!P11)</f>
-        <v/>
-      </c>
-      <c r="C13" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M11)*(Релизы!$D$5:$D$9&gt;=Бэклог!M11)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="220">
-        <f>IF(AND(B13&lt;&gt;"",C13&gt;0),C13-B13,"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="186">
-        <f>IF(D13="",NA(),D13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="218">
-        <f>IF(Бэклог!A12="","",Бэклог!A12)</f>
-        <v/>
-      </c>
-      <c r="B14" s="219">
-        <f>IF(Бэклог!P12="","",Бэклог!P12)</f>
-        <v/>
-      </c>
-      <c r="C14" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M12)*(Релизы!$D$5:$D$9&gt;=Бэклог!M12)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="220">
-        <f>IF(AND(B14&lt;&gt;"",C14&gt;0),C14-B14,"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="186">
-        <f>IF(D14="",NA(),D14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="218">
-        <f>IF(Бэклог!A13="","",Бэклог!A13)</f>
-        <v/>
-      </c>
-      <c r="B15" s="219">
-        <f>IF(Бэклог!P13="","",Бэклог!P13)</f>
-        <v/>
-      </c>
-      <c r="C15" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M13)*(Релизы!$D$5:$D$9&gt;=Бэклог!M13)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="220">
-        <f>IF(AND(B15&lt;&gt;"",C15&gt;0),C15-B15,"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="186">
-        <f>IF(D15="",NA(),D15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="218">
-        <f>IF(Бэклог!A14="","",Бэклог!A14)</f>
-        <v/>
-      </c>
-      <c r="B16" s="219">
-        <f>IF(Бэклог!P14="","",Бэклог!P14)</f>
-        <v/>
-      </c>
-      <c r="C16" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M14)*(Релизы!$D$5:$D$9&gt;=Бэклог!M14)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="220">
-        <f>IF(AND(B16&lt;&gt;"",C16&gt;0),C16-B16,"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="186">
-        <f>IF(D16="",NA(),D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="218">
-        <f>IF(Бэклог!A15="","",Бэклог!A15)</f>
-        <v/>
-      </c>
-      <c r="B17" s="219">
-        <f>IF(Бэклог!P15="","",Бэклог!P15)</f>
-        <v/>
-      </c>
-      <c r="C17" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M15)*(Релизы!$D$5:$D$9&gt;=Бэклог!M15)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="220">
-        <f>IF(AND(B17&lt;&gt;"",C17&gt;0),C17-B17,"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="186">
-        <f>IF(D17="",NA(),D17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="218">
-        <f>IF(Бэклог!A16="","",Бэклог!A16)</f>
-        <v/>
-      </c>
-      <c r="B18" s="219">
-        <f>IF(Бэклог!P16="","",Бэклог!P16)</f>
-        <v/>
-      </c>
-      <c r="C18" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M16)*(Релизы!$D$5:$D$9&gt;=Бэклог!M16)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="220">
-        <f>IF(AND(B18&lt;&gt;"",C18&gt;0),C18-B18,"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="186">
-        <f>IF(D18="",NA(),D18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="218">
-        <f>IF(Бэклог!A17="","",Бэклог!A17)</f>
-        <v/>
-      </c>
-      <c r="B19" s="219">
-        <f>IF(Бэклог!P17="","",Бэклог!P17)</f>
-        <v/>
-      </c>
-      <c r="C19" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M17)*(Релизы!$D$5:$D$9&gt;=Бэклог!M17)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="220">
-        <f>IF(AND(B19&lt;&gt;"",C19&gt;0),C19-B19,"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="186">
-        <f>IF(D19="",NA(),D19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="218">
-        <f>IF(Бэклог!A18="","",Бэклог!A18)</f>
-        <v/>
-      </c>
-      <c r="B20" s="219">
-        <f>IF(Бэклог!P18="","",Бэклог!P18)</f>
-        <v/>
-      </c>
-      <c r="C20" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M18)*(Релизы!$D$5:$D$9&gt;=Бэклог!M18)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="220">
-        <f>IF(AND(B20&lt;&gt;"",C20&gt;0),C20-B20,"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="186">
-        <f>IF(D20="",NA(),D20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="218">
-        <f>IF(Бэклог!A19="","",Бэклог!A19)</f>
-        <v/>
-      </c>
-      <c r="B21" s="219">
-        <f>IF(Бэклог!P19="","",Бэклог!P19)</f>
-        <v/>
-      </c>
-      <c r="C21" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M19)*(Релизы!$D$5:$D$9&gt;=Бэклог!M19)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="220">
-        <f>IF(AND(B21&lt;&gt;"",C21&gt;0),C21-B21,"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="186">
-        <f>IF(D21="",NA(),D21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="218">
-        <f>IF(Бэклог!A20="","",Бэклог!A20)</f>
-        <v/>
-      </c>
-      <c r="B22" s="219">
-        <f>IF(Бэклог!P20="","",Бэклог!P20)</f>
-        <v/>
-      </c>
-      <c r="C22" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M20)*(Релизы!$D$5:$D$9&gt;=Бэклог!M20)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="220">
-        <f>IF(AND(B22&lt;&gt;"",C22&gt;0),C22-B22,"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="186">
-        <f>IF(D22="",NA(),D22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="218">
-        <f>IF(Бэклог!A21="","",Бэклог!A21)</f>
-        <v/>
-      </c>
-      <c r="B23" s="219">
-        <f>IF(Бэклог!P21="","",Бэклог!P21)</f>
-        <v/>
-      </c>
-      <c r="C23" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M21)*(Релизы!$D$5:$D$9&gt;=Бэклог!M21)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D23" s="220">
-        <f>IF(AND(B23&lt;&gt;"",C23&gt;0),C23-B23,"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="186">
-        <f>IF(D23="",NA(),D23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="218">
-        <f>IF(Бэклог!A22="","",Бэклог!A22)</f>
-        <v/>
-      </c>
-      <c r="B24" s="219">
-        <f>IF(Бэклог!P22="","",Бэклог!P22)</f>
-        <v/>
-      </c>
-      <c r="C24" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M22)*(Релизы!$D$5:$D$9&gt;=Бэклог!M22)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D24" s="220">
-        <f>IF(AND(B24&lt;&gt;"",C24&gt;0),C24-B24,"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="186">
-        <f>IF(D24="",NA(),D24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="218">
-        <f>IF(Бэклог!A23="","",Бэклог!A23)</f>
-        <v/>
-      </c>
-      <c r="B25" s="219">
-        <f>IF(Бэклог!P23="","",Бэклог!P23)</f>
-        <v/>
-      </c>
-      <c r="C25" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M23)*(Релизы!$D$5:$D$9&gt;=Бэклог!M23)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="220">
-        <f>IF(AND(B25&lt;&gt;"",C25&gt;0),C25-B25,"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="186">
-        <f>IF(D25="",NA(),D25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="218">
-        <f>IF(Бэклог!A24="","",Бэклог!A24)</f>
-        <v/>
-      </c>
-      <c r="B26" s="219">
-        <f>IF(Бэклог!P24="","",Бэклог!P24)</f>
-        <v/>
-      </c>
-      <c r="C26" s="219">
-        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M24)*(Релизы!$D$5:$D$9&gt;=Бэклог!M24)*Релизы!$E$5:$E$9),0)</f>
-        <v/>
-      </c>
-      <c r="D26" s="220">
-        <f>IF(AND(B26&lt;&gt;"",C26&gt;0),C26-B26,"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="221">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="186">
-        <f>IF(D26="",NA(),D26)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -45024,6 +45257,615 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="5"/>
+    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" customHeight="1">
+      <c r="A1" s="213" t="inlineStr">
+        <is>
+          <t>Time to Market (TTM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="214" t="inlineStr">
+        <is>
+          <t>TTM = дата релиза − дата взятия задачи в работу. Цель — 15 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Цель TTM (дн):</t>
+        </is>
+      </c>
+      <c r="C3" s="215" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Средний TTM (дн):</t>
+        </is>
+      </c>
+      <c r="C4" s="216">
+        <f>IFERROR(AVERAGEIF(D7:D26,"&gt;=0"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="27.6" customHeight="1">
+      <c r="A6" s="217" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="B6" s="217" t="inlineStr">
+        <is>
+          <t>В работу</t>
+        </is>
+      </c>
+      <c r="C6" s="217" t="inlineStr">
+        <is>
+          <t>Дата релиза</t>
+        </is>
+      </c>
+      <c r="D6" s="217" t="inlineStr">
+        <is>
+          <t>TTM (дн)</t>
+        </is>
+      </c>
+      <c r="E6" s="217" t="inlineStr">
+        <is>
+          <t>Цель (дн)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TTM (дн)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="218">
+        <f>IF(Бэклог!A5="","",Бэклог!A5)</f>
+        <v/>
+      </c>
+      <c r="B7" s="219">
+        <f>IF(Бэклог!P5="","",Бэклог!P5)</f>
+        <v/>
+      </c>
+      <c r="C7" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M5)*(Релизы!$D$5:$D$9&gt;=Бэклог!M5)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="220">
+        <f>IF(AND(B7&lt;&gt;"",C7&gt;0),C7-B7,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F7" s="186">
+        <f>IF(D7="",NA(),D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="218">
+        <f>IF(Бэклог!A6="","",Бэклог!A6)</f>
+        <v/>
+      </c>
+      <c r="B8" s="219">
+        <f>IF(Бэклог!P6="","",Бэклог!P6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M6)*(Релизы!$D$5:$D$9&gt;=Бэклог!M6)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="220">
+        <f>IF(AND(B8&lt;&gt;"",C8&gt;0),C8-B8,"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F8" s="186">
+        <f>IF(D8="",NA(),D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="218">
+        <f>IF(Бэклог!A7="","",Бэклог!A7)</f>
+        <v/>
+      </c>
+      <c r="B9" s="219">
+        <f>IF(Бэклог!P7="","",Бэклог!P7)</f>
+        <v/>
+      </c>
+      <c r="C9" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M7)*(Релизы!$D$5:$D$9&gt;=Бэклог!M7)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="220">
+        <f>IF(AND(B9&lt;&gt;"",C9&gt;0),C9-B9,"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F9" s="186">
+        <f>IF(D9="",NA(),D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="218">
+        <f>IF(Бэклог!A8="","",Бэклог!A8)</f>
+        <v/>
+      </c>
+      <c r="B10" s="219">
+        <f>IF(Бэклог!P8="","",Бэклог!P8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M8)*(Релизы!$D$5:$D$9&gt;=Бэклог!M8)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="220">
+        <f>IF(AND(B10&lt;&gt;"",C10&gt;0),C10-B10,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F10" s="186">
+        <f>IF(D10="",NA(),D10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="218">
+        <f>IF(Бэклог!A9="","",Бэклог!A9)</f>
+        <v/>
+      </c>
+      <c r="B11" s="219">
+        <f>IF(Бэклог!P9="","",Бэклог!P9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M9)*(Релизы!$D$5:$D$9&gt;=Бэклог!M9)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="220">
+        <f>IF(AND(B11&lt;&gt;"",C11&gt;0),C11-B11,"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F11" s="186">
+        <f>IF(D11="",NA(),D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="218">
+        <f>IF(Бэклог!A10="","",Бэклог!A10)</f>
+        <v/>
+      </c>
+      <c r="B12" s="219">
+        <f>IF(Бэклог!P10="","",Бэклог!P10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M10)*(Релизы!$D$5:$D$9&gt;=Бэклог!M10)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="220">
+        <f>IF(AND(B12&lt;&gt;"",C12&gt;0),C12-B12,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F12" s="186">
+        <f>IF(D12="",NA(),D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="218">
+        <f>IF(Бэклог!A11="","",Бэклог!A11)</f>
+        <v/>
+      </c>
+      <c r="B13" s="219">
+        <f>IF(Бэклог!P11="","",Бэклог!P11)</f>
+        <v/>
+      </c>
+      <c r="C13" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M11)*(Релизы!$D$5:$D$9&gt;=Бэклог!M11)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="220">
+        <f>IF(AND(B13&lt;&gt;"",C13&gt;0),C13-B13,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F13" s="186">
+        <f>IF(D13="",NA(),D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="218">
+        <f>IF(Бэклог!A12="","",Бэклог!A12)</f>
+        <v/>
+      </c>
+      <c r="B14" s="219">
+        <f>IF(Бэклог!P12="","",Бэклог!P12)</f>
+        <v/>
+      </c>
+      <c r="C14" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M12)*(Релизы!$D$5:$D$9&gt;=Бэклог!M12)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="220">
+        <f>IF(AND(B14&lt;&gt;"",C14&gt;0),C14-B14,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F14" s="186">
+        <f>IF(D14="",NA(),D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="218">
+        <f>IF(Бэклог!A13="","",Бэклог!A13)</f>
+        <v/>
+      </c>
+      <c r="B15" s="219">
+        <f>IF(Бэклог!P13="","",Бэклог!P13)</f>
+        <v/>
+      </c>
+      <c r="C15" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M13)*(Релизы!$D$5:$D$9&gt;=Бэклог!M13)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="220">
+        <f>IF(AND(B15&lt;&gt;"",C15&gt;0),C15-B15,"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F15" s="186">
+        <f>IF(D15="",NA(),D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="218">
+        <f>IF(Бэклог!A14="","",Бэклог!A14)</f>
+        <v/>
+      </c>
+      <c r="B16" s="219">
+        <f>IF(Бэклог!P14="","",Бэклог!P14)</f>
+        <v/>
+      </c>
+      <c r="C16" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M14)*(Релизы!$D$5:$D$9&gt;=Бэклог!M14)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="220">
+        <f>IF(AND(B16&lt;&gt;"",C16&gt;0),C16-B16,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F16" s="186">
+        <f>IF(D16="",NA(),D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="218">
+        <f>IF(Бэклог!A15="","",Бэклог!A15)</f>
+        <v/>
+      </c>
+      <c r="B17" s="219">
+        <f>IF(Бэклог!P15="","",Бэклог!P15)</f>
+        <v/>
+      </c>
+      <c r="C17" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M15)*(Релизы!$D$5:$D$9&gt;=Бэклог!M15)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="220">
+        <f>IF(AND(B17&lt;&gt;"",C17&gt;0),C17-B17,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F17" s="186">
+        <f>IF(D17="",NA(),D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="218">
+        <f>IF(Бэклог!A16="","",Бэклог!A16)</f>
+        <v/>
+      </c>
+      <c r="B18" s="219">
+        <f>IF(Бэклог!P16="","",Бэклог!P16)</f>
+        <v/>
+      </c>
+      <c r="C18" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M16)*(Релизы!$D$5:$D$9&gt;=Бэклог!M16)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="220">
+        <f>IF(AND(B18&lt;&gt;"",C18&gt;0),C18-B18,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F18" s="186">
+        <f>IF(D18="",NA(),D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="218">
+        <f>IF(Бэклог!A17="","",Бэклог!A17)</f>
+        <v/>
+      </c>
+      <c r="B19" s="219">
+        <f>IF(Бэклог!P17="","",Бэклог!P17)</f>
+        <v/>
+      </c>
+      <c r="C19" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M17)*(Релизы!$D$5:$D$9&gt;=Бэклог!M17)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="220">
+        <f>IF(AND(B19&lt;&gt;"",C19&gt;0),C19-B19,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F19" s="186">
+        <f>IF(D19="",NA(),D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="218">
+        <f>IF(Бэклог!A18="","",Бэклог!A18)</f>
+        <v/>
+      </c>
+      <c r="B20" s="219">
+        <f>IF(Бэклог!P18="","",Бэклог!P18)</f>
+        <v/>
+      </c>
+      <c r="C20" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M18)*(Релизы!$D$5:$D$9&gt;=Бэклог!M18)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="220">
+        <f>IF(AND(B20&lt;&gt;"",C20&gt;0),C20-B20,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F20" s="186">
+        <f>IF(D20="",NA(),D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="218">
+        <f>IF(Бэклог!A19="","",Бэклог!A19)</f>
+        <v/>
+      </c>
+      <c r="B21" s="219">
+        <f>IF(Бэклог!P19="","",Бэклог!P19)</f>
+        <v/>
+      </c>
+      <c r="C21" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M19)*(Релизы!$D$5:$D$9&gt;=Бэклог!M19)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="220">
+        <f>IF(AND(B21&lt;&gt;"",C21&gt;0),C21-B21,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F21" s="186">
+        <f>IF(D21="",NA(),D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="218">
+        <f>IF(Бэклог!A20="","",Бэклог!A20)</f>
+        <v/>
+      </c>
+      <c r="B22" s="219">
+        <f>IF(Бэклог!P20="","",Бэклог!P20)</f>
+        <v/>
+      </c>
+      <c r="C22" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M20)*(Релизы!$D$5:$D$9&gt;=Бэклог!M20)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="220">
+        <f>IF(AND(B22&lt;&gt;"",C22&gt;0),C22-B22,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F22" s="186">
+        <f>IF(D22="",NA(),D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="218">
+        <f>IF(Бэклог!A21="","",Бэклог!A21)</f>
+        <v/>
+      </c>
+      <c r="B23" s="219">
+        <f>IF(Бэклог!P21="","",Бэклог!P21)</f>
+        <v/>
+      </c>
+      <c r="C23" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M21)*(Релизы!$D$5:$D$9&gt;=Бэклог!M21)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="220">
+        <f>IF(AND(B23&lt;&gt;"",C23&gt;0),C23-B23,"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F23" s="186">
+        <f>IF(D23="",NA(),D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="218">
+        <f>IF(Бэклог!A22="","",Бэклог!A22)</f>
+        <v/>
+      </c>
+      <c r="B24" s="219">
+        <f>IF(Бэклог!P22="","",Бэклог!P22)</f>
+        <v/>
+      </c>
+      <c r="C24" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M22)*(Релизы!$D$5:$D$9&gt;=Бэклог!M22)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="220">
+        <f>IF(AND(B24&lt;&gt;"",C24&gt;0),C24-B24,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F24" s="186">
+        <f>IF(D24="",NA(),D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="218">
+        <f>IF(Бэклог!A23="","",Бэклог!A23)</f>
+        <v/>
+      </c>
+      <c r="B25" s="219">
+        <f>IF(Бэклог!P23="","",Бэклог!P23)</f>
+        <v/>
+      </c>
+      <c r="C25" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M23)*(Релизы!$D$5:$D$9&gt;=Бэклог!M23)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="220">
+        <f>IF(AND(B25&lt;&gt;"",C25&gt;0),C25-B25,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F25" s="186">
+        <f>IF(D25="",NA(),D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="218">
+        <f>IF(Бэклог!A24="","",Бэклог!A24)</f>
+        <v/>
+      </c>
+      <c r="B26" s="219">
+        <f>IF(Бэклог!P24="","",Бэклог!P24)</f>
+        <v/>
+      </c>
+      <c r="C26" s="219">
+        <f>IFERROR(SUMPRODUCT((Релизы!$C$5:$C$9&lt;=Бэклог!M24)*(Релизы!$D$5:$D$9&gt;=Бэклог!M24)*Релизы!$E$5:$E$9),0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="220">
+        <f>IF(AND(B26&lt;&gt;"",C26&gt;0),C26-B26,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="221">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="F26" s="186">
+        <f>IF(D26="",NA(),D26)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
